--- a/data/merged/2026-10-08/MERGED_JP_Mite-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_JP_Mite-Vacuum_2026-10-08.xlsx
@@ -5755,13 +5755,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5799,13 +5799,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6195,13 +6195,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6283,13 +6283,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6762,314 +6762,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Product 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId44" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Product 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId45" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Product 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId46" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Product 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Product 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7395,7 +7087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -12412,40 +12104,40 @@
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>B016UAX3VQ</t>
+          <t>B0D7HWNDXS</t>
         </is>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>パナソニック(Panasonic)</t>
+          <t>EFSHREE</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%91%E3%83%8A%E3%82%BD%E3%83%8B%E3%83%83%E3%82%AF/page/9050EF98-FCF6-43FC-8443-62F3CF3A646C?lp_asin=B016UAX3VQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=EFSHREE</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>松下 吸尘器 纸袋式 带室内灰尘探测传感器 粉色香槟 MC-DF500G-P</t>
+          <t>EFSHREE 布団掃除機 布団清洁机 除螨清洁机 布団干燥机 UV灯 HEPA滤网 温风 10000Pa 超轻1.25千克 适用花粉 床 沙发 家用车载 (白色)</t>
         </is>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B016UAX3VQ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D7HWNDXS?psc=1</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41UdWx+bhwL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31+u94XQLbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>B016UAX3VQ</t>
+          <t>B0D7HWNDXS</t>
         </is>
       </c>
       <c r="M22" s="12" t="inlineStr">
@@ -12459,13 +12151,13 @@
         </is>
       </c>
       <c r="O22" s="13">
-        <v>125432</v>
+        <v>19757</v>
       </c>
       <c r="P22" s="13">
-        <v>-34198</v>
+        <v>10776</v>
       </c>
       <c r="Q22" s="14">
-        <v>-0.37</v>
+        <v>0.35</v>
       </c>
       <c r="R22" s="15" t="inlineStr">
         <is>
@@ -12474,50 +12166,62 @@
       </c>
       <c r="S22" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T22" s="13">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="U22" s="14">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V22" s="13">
-        <v>428800</v>
-      </c>
-      <c r="W22" s="13"/>
-      <c r="X22" s="13"/>
+        <v>420564</v>
+      </c>
+      <c r="W22" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X22" s="13">
+        <v>229000</v>
+      </c>
       <c r="Y22" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="13">
-        <v>26800</v>
+        <v>4164</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
-      <c r="AC22" s="13">
-        <v>7</v>
-      </c>
+      <c r="AC22" s="13"/>
       <c r="AD22" s="17">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="AE22" s="13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF22" s="18">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AG22" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="13"/>
+        <v>0.039599999999999996</v>
+      </c>
+      <c r="AH22" s="13">
+        <v>472</v>
+      </c>
       <c r="AI22" s="14">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AJ22"/>
-      <c r="AK22" s="11"/>
-      <c r="AL22" s="17"/>
+      <c r="AK22" s="11" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AL22" s="17">
+        <v>790</v>
+      </c>
       <c r="AM22" s="11" t="inlineStr">
         <is>
           <t>FBA</t>
@@ -12527,14 +12231,14 @@
       <c r="AO22" s="11"/>
       <c r="AP22"/>
       <c r="AQ22" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR22" s="17">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AS22" s="12" t="inlineStr">
         <is>
-          <t>パル商店【適格請求書発行事業者】</t>
+          <t>YFS-JP</t>
         </is>
       </c>
       <c r="AT22" s="11" t="inlineStr">
@@ -12544,17 +12248,17 @@
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV22" s="12" t="inlineStr">
         <is>
-          <t>新宿区 東京都 1600023 JP</t>
+          <t>WangTing Town, XiangCheng District Suzhou China 215155 CN</t>
         </is>
       </c>
       <c r="AW22" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24MAWLD4IUCCX</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2DFDWLWCIL47K</t>
         </is>
       </c>
       <c r="AX22" s="11"/>
@@ -12567,11 +12271,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD22" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD22" s="11"/>
       <c r="BE22" s="11"/>
       <c r="BF22" s="11"/>
       <c r="BG22" s="11"/>
@@ -12579,25 +12279,45 @@
       <c r="BI22" s="20"/>
       <c r="BJ22" s="20" t="inlineStr">
         <is>
-          <t>3100 グラム</t>
-        </is>
-      </c>
-      <c r="BK22" s="20"/>
+          <t>1.27 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK22" s="20" t="inlineStr">
+        <is>
+          <t>1.27 kg</t>
+        </is>
+      </c>
       <c r="BL22" s="20" t="inlineStr">
         <is>
-          <t>43.1 x 32.9 x 22.6 cm</t>
-        </is>
-      </c>
-      <c r="BM22" s="20" t="inlineStr">
-        <is>
-          <t>43.10 x 32.90 x 22.60 cm</t>
-        </is>
-      </c>
-      <c r="BN22" s="20"/>
-      <c r="BO22" s="20"/>
-      <c r="BP22" s="20"/>
-      <c r="BQ22" s="20"/>
-      <c r="BR22" s="11"/>
+          <t>25長さ x 32幅 x 14高さ cm</t>
+        </is>
+      </c>
+      <c r="BM22" s="20"/>
+      <c r="BN22" s="20" t="inlineStr">
+        <is>
+          <t>1.52 kg</t>
+        </is>
+      </c>
+      <c r="BO22" s="20" t="inlineStr">
+        <is>
+          <t>1.52 kg</t>
+        </is>
+      </c>
+      <c r="BP22" s="20" t="inlineStr">
+        <is>
+          <t>35.5 x 28.3 x 14.5 cm</t>
+        </is>
+      </c>
+      <c r="BQ22" s="20" t="inlineStr">
+        <is>
+          <t>35.50 x 28.30 x 14.50 cm</t>
+        </is>
+      </c>
+      <c r="BR22" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
@@ -12606,40 +12326,40 @@
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>B0D7HWNDXS</t>
+          <t>B07RT2QD4C</t>
         </is>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>EFSHREE</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=EFSHREE</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B07RT2QD4C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>EFSHREE 布団掃除機 布団清洁机 除螨清洁机 布団干燥机 UV灯 HEPA滤网 温风 10000Pa 超轻1.25千克 适用花粉 床 沙发 家用车载 (白色)</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 全国适用(电源 AC100V 50/60hz) 手持式 强力 被褥清洁器 搭载螨虫和簸箕 拍打 约6,500次/分钟 IC-FAC3</t>
         </is>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D7HWNDXS?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B07RT2QD4C?psc=1</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31+u94XQLbL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51aZRLkyoaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>B0D7HWNDXS</t>
+          <t>B07RT2QD4C</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
@@ -12653,13 +12373,13 @@
         </is>
       </c>
       <c r="O23" s="13">
-        <v>19757</v>
+        <v>88041</v>
       </c>
       <c r="P23" s="13">
-        <v>10776</v>
+        <v>2707</v>
       </c>
       <c r="Q23" s="14">
-        <v>0.35</v>
+        <v>0.03</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -12668,61 +12388,57 @@
       </c>
       <c r="S23" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T23" s="13">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="U23" s="14">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="V23" s="13">
-        <v>420564</v>
-      </c>
-      <c r="W23" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X23" s="13">
-        <v>229000</v>
-      </c>
+        <v>324000</v>
+      </c>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
       <c r="Y23" s="17">
         <v>1</v>
       </c>
       <c r="Z23" s="13">
-        <v>4164</v>
+        <v>12000</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
-      <c r="AC23" s="13"/>
+      <c r="AC23" s="13">
+        <v>57</v>
+      </c>
       <c r="AD23" s="17">
-        <v>86</v>
+        <v>2511</v>
       </c>
       <c r="AE23" s="13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="18">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AG23" s="19">
-        <v>0.039599999999999996</v>
+        <v>0</v>
       </c>
       <c r="AH23" s="13">
-        <v>472</v>
+        <v>675</v>
       </c>
       <c r="AI23" s="14">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="AJ23"/>
       <c r="AK23" s="11" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2019-05-20</t>
         </is>
       </c>
       <c r="AL23" s="17">
-        <v>790</v>
+        <v>2697</v>
       </c>
       <c r="AM23" s="11" t="inlineStr">
         <is>
@@ -12740,7 +12456,7 @@
       </c>
       <c r="AS23" s="12" t="inlineStr">
         <is>
-          <t>YFS-JP</t>
+          <t>【公式】halfilm market - インボイス対応 -</t>
         </is>
       </c>
       <c r="AT23" s="11" t="inlineStr">
@@ -12750,17 +12466,17 @@
       </c>
       <c r="AU23" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV23" s="12" t="inlineStr">
         <is>
-          <t>WangTing Town, XiangCheng District Suzhou China 215155 CN</t>
+          <t>栃木県 3213226 JP</t>
         </is>
       </c>
       <c r="AW23" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2DFDWLWCIL47K</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A28J8GQ3UQRK50</t>
         </is>
       </c>
       <c r="AX23" s="11"/>
@@ -12773,7 +12489,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD23" s="11"/>
+      <c r="BD23" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE23" s="11"/>
       <c r="BF23" s="11"/>
       <c r="BG23" s="11"/>
@@ -12781,43 +12501,47 @@
       <c r="BI23" s="20"/>
       <c r="BJ23" s="20" t="inlineStr">
         <is>
-          <t>1.27 Kilograms</t>
+          <t>1.6 kg</t>
         </is>
       </c>
       <c r="BK23" s="20" t="inlineStr">
         <is>
-          <t>1.27 kg</t>
+          <t>1.60 kg</t>
         </is>
       </c>
       <c r="BL23" s="20" t="inlineStr">
         <is>
-          <t>25長さ x 32幅 x 14高さ cm</t>
-        </is>
-      </c>
-      <c r="BM23" s="20"/>
+          <t>45.9 x 25 x 21.2 cm</t>
+        </is>
+      </c>
+      <c r="BM23" s="20" t="inlineStr">
+        <is>
+          <t>45.90 x 25.00 x 21.20 cm</t>
+        </is>
+      </c>
       <c r="BN23" s="20" t="inlineStr">
         <is>
-          <t>1.52 kg</t>
+          <t>2.45 kg</t>
         </is>
       </c>
       <c r="BO23" s="20" t="inlineStr">
         <is>
-          <t>1.52 kg</t>
+          <t>2.45 kg</t>
         </is>
       </c>
       <c r="BP23" s="20" t="inlineStr">
         <is>
-          <t>35.5 x 28.3 x 14.5 cm</t>
+          <t>46.2 x 28.3 x 18.2 cm</t>
         </is>
       </c>
       <c r="BQ23" s="20" t="inlineStr">
         <is>
-          <t>35.50 x 28.30 x 14.50 cm</t>
+          <t>46.20 x 28.30 x 18.20 cm</t>
         </is>
       </c>
       <c r="BR23" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -12828,40 +12552,40 @@
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>B07RT2QD4C</t>
+          <t>B0D1XQPH2V</t>
         </is>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B07RT2QD4C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JIGOO</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 全国适用(电源 AC100V 50/60hz) 手持式 强力 被褥清洁器 搭载螨虫和簸箕 拍打 约6,500次/分钟 IC-FAC3</t>
+          <t>JIGOO J300 布団クリーナー ダニフィルター分離設計 500W 布団用掃除機 13Kpa 強力吸引 ウイルス除去 UV除菌 アレルゲン対策 55°C加熱 熱風乾燥 ふとん掃除機</t>
         </is>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07RT2QD4C?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D1XQPH2V?psc=1</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51aZRLkyoaL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81kvopazcOL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>B07RT2QD4C</t>
+          <t>B0D1XQPH2V</t>
         </is>
       </c>
       <c r="M24" s="12" t="inlineStr">
@@ -12875,13 +12599,13 @@
         </is>
       </c>
       <c r="O24" s="13">
-        <v>88041</v>
+        <v>205321</v>
       </c>
       <c r="P24" s="13">
-        <v>2707</v>
+        <v>-75535</v>
       </c>
       <c r="Q24" s="14">
-        <v>0.03</v>
+        <v>-0.58</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -12890,17 +12614,17 @@
       </c>
       <c r="S24" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T24" s="13">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="U24" s="14">
-        <v>0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="V24" s="13">
-        <v>324000</v>
+        <v>302583</v>
       </c>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
@@ -12908,39 +12632,37 @@
         <v>1</v>
       </c>
       <c r="Z24" s="13">
-        <v>12000</v>
+        <v>17799</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
-      <c r="AC24" s="13">
-        <v>57</v>
-      </c>
+      <c r="AC24" s="13"/>
       <c r="AD24" s="17">
-        <v>2511</v>
+        <v>110</v>
       </c>
       <c r="AE24" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" s="18">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG24" s="19">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="AH24" s="13">
         <v>675</v>
       </c>
       <c r="AI24" s="14">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="AJ24"/>
       <c r="AK24" s="11" t="inlineStr">
         <is>
-          <t>2019-05-20</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AL24" s="17">
-        <v>2697</v>
+        <v>903</v>
       </c>
       <c r="AM24" s="11" t="inlineStr">
         <is>
@@ -12951,14 +12673,14 @@
       <c r="AO24" s="11"/>
       <c r="AP24"/>
       <c r="AQ24" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR24" s="17">
         <v>1</v>
       </c>
       <c r="AS24" s="12" t="inlineStr">
         <is>
-          <t>【公式】halfilm market - インボイス対応 -</t>
+          <t>Qifan shop</t>
         </is>
       </c>
       <c r="AT24" s="11" t="inlineStr">
@@ -12968,21 +12690,25 @@
       </c>
       <c r="AU24" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV24" s="12" t="inlineStr">
         <is>
-          <t>栃木県 3213226 JP</t>
+          <t>Tuen Mun Hong Kong 999077 HK</t>
         </is>
       </c>
       <c r="AW24" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A28J8GQ3UQRK50</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UV5G74OMRQ0L</t>
         </is>
       </c>
       <c r="AX24" s="11"/>
-      <c r="AY24" s="11"/>
+      <c r="AY24" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ24" s="11"/>
       <c r="BA24" s="11"/>
       <c r="BB24" s="11"/>
@@ -13000,45 +12726,45 @@
       <c r="BF24" s="11"/>
       <c r="BG24" s="11"/>
       <c r="BH24" s="12"/>
-      <c r="BI24" s="20"/>
+      <c r="BI24" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ24" s="20" t="inlineStr">
         <is>
-          <t>1.6 kg</t>
+          <t>1.85 kg</t>
         </is>
       </c>
       <c r="BK24" s="20" t="inlineStr">
         <is>
-          <t>1.60 kg</t>
+          <t>1.85 kg</t>
         </is>
       </c>
       <c r="BL24" s="20" t="inlineStr">
         <is>
-          <t>45.9 x 25 x 21.2 cm</t>
-        </is>
-      </c>
-      <c r="BM24" s="20" t="inlineStr">
-        <is>
-          <t>45.90 x 25.00 x 21.20 cm</t>
-        </is>
-      </c>
+          <t>24.7長さ x 21幅 x 30.7高さ cm</t>
+        </is>
+      </c>
+      <c r="BM24" s="20"/>
       <c r="BN24" s="20" t="inlineStr">
         <is>
-          <t>2.45 kg</t>
+          <t>2.38 kg</t>
         </is>
       </c>
       <c r="BO24" s="20" t="inlineStr">
         <is>
-          <t>2.45 kg</t>
+          <t>2.38 kg</t>
         </is>
       </c>
       <c r="BP24" s="20" t="inlineStr">
         <is>
-          <t>46.2 x 28.3 x 18.2 cm</t>
+          <t>34.4 x 28 x 25.6 cm</t>
         </is>
       </c>
       <c r="BQ24" s="20" t="inlineStr">
         <is>
-          <t>46.20 x 28.30 x 18.20 cm</t>
+          <t>34.40 x 28.00 x 25.60 cm</t>
         </is>
       </c>
       <c r="BR24" s="11" t="inlineStr">
@@ -13054,40 +12780,40 @@
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>B0D1XQPH2V</t>
+          <t>B01GUPMJMA</t>
         </is>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JIGOO</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B01GUPMJMA&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>JIGOO J300 布団クリーナー ダニフィルター分離設計 500W 布団用掃除機 13Kpa 強力吸引 ウイルス除去 UV除菌 アレルゲン対策 55°C加熱 熱風乾燥 ふとん掃除機</t>
+          <t>IRIS OHYAMA 超吸引 被褥吸尘器 白色 IC-FAC2</t>
         </is>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D1XQPH2V?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B01GUPMJMA?psc=1</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81kvopazcOL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31aFWaIaVDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>B0D1XQPH2V</t>
+          <t>B01GUPMJMA</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
@@ -13101,13 +12827,13 @@
         </is>
       </c>
       <c r="O25" s="13">
-        <v>205321</v>
+        <v>50191</v>
       </c>
       <c r="P25" s="13">
-        <v>-75535</v>
+        <v>-160820</v>
       </c>
       <c r="Q25" s="14">
-        <v>-0.58</v>
+        <v>-3.34</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -13116,17 +12842,17 @@
       </c>
       <c r="S25" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T25" s="13">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="U25" s="14">
-        <v>-0.21</v>
+        <v>0.07</v>
       </c>
       <c r="V25" s="13">
-        <v>302583</v>
+        <v>236740</v>
       </c>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
@@ -13134,37 +12860,39 @@
         <v>1</v>
       </c>
       <c r="Z25" s="13">
-        <v>17799</v>
+        <v>8455</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
-      <c r="AC25" s="13"/>
+      <c r="AC25" s="13">
+        <v>81</v>
+      </c>
       <c r="AD25" s="17">
-        <v>110</v>
+        <v>1902</v>
       </c>
       <c r="AE25" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF25" s="18">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG25" s="19">
-        <v>0.0588</v>
+        <v>0.10710000000000001</v>
       </c>
       <c r="AH25" s="13">
         <v>675</v>
       </c>
       <c r="AI25" s="14">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="AJ25"/>
       <c r="AK25" s="11" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2016-06-11</t>
         </is>
       </c>
       <c r="AL25" s="17">
-        <v>903</v>
+        <v>3770</v>
       </c>
       <c r="AM25" s="11" t="inlineStr">
         <is>
@@ -13175,14 +12903,14 @@
       <c r="AO25" s="11"/>
       <c r="AP25"/>
       <c r="AQ25" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR25" s="17">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AS25" s="12" t="inlineStr">
         <is>
-          <t>Qifan shop</t>
+          <t>FASネット部門(古物商許可、インボイス制度登録)</t>
         </is>
       </c>
       <c r="AT25" s="11" t="inlineStr">
@@ -13192,17 +12920,17 @@
       </c>
       <c r="AU25" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV25" s="12" t="inlineStr">
         <is>
-          <t>Tuen Mun Hong Kong 999077 HK</t>
+          <t>相田６－９－１３－２</t>
         </is>
       </c>
       <c r="AW25" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UV5G74OMRQ0L</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR8B5CKEPZWTA</t>
         </is>
       </c>
       <c r="AX25" s="11"/>
@@ -13214,11 +12942,7 @@
       <c r="AZ25" s="11"/>
       <c r="BA25" s="11"/>
       <c r="BB25" s="11"/>
-      <c r="BC25" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC25" s="11"/>
       <c r="BD25" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13230,43 +12954,43 @@
       <c r="BH25" s="12"/>
       <c r="BI25" s="20" t="inlineStr">
         <is>
-          <t>Amazon おすすめ</t>
+          <t>ic-fac2</t>
         </is>
       </c>
       <c r="BJ25" s="20" t="inlineStr">
         <is>
-          <t>1.85 kg</t>
+          <t>1.6 Kilograms</t>
         </is>
       </c>
       <c r="BK25" s="20" t="inlineStr">
         <is>
-          <t>1.85 kg</t>
+          <t>1.60 kg</t>
         </is>
       </c>
       <c r="BL25" s="20" t="inlineStr">
         <is>
-          <t>24.7長さ x 21幅 x 30.7高さ cm</t>
+          <t>45.9長さ x 25幅 x 21.2高さ cm</t>
         </is>
       </c>
       <c r="BM25" s="20"/>
       <c r="BN25" s="20" t="inlineStr">
         <is>
-          <t>2.38 kg</t>
+          <t>2.56 kg</t>
         </is>
       </c>
       <c r="BO25" s="20" t="inlineStr">
         <is>
-          <t>2.38 kg</t>
+          <t>2.56 kg</t>
         </is>
       </c>
       <c r="BP25" s="20" t="inlineStr">
         <is>
-          <t>34.4 x 28 x 25.6 cm</t>
+          <t>46.4 x 28.4 x 18.4 cm</t>
         </is>
       </c>
       <c r="BQ25" s="20" t="inlineStr">
         <is>
-          <t>34.40 x 28.00 x 25.60 cm</t>
+          <t>46.40 x 28.40 x 18.40 cm</t>
         </is>
       </c>
       <c r="BR25" s="11" t="inlineStr">
@@ -13282,40 +13006,40 @@
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>B01GUPMJMA</t>
+          <t>B0F4WKGDNF</t>
         </is>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B01GUPMJMA&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0F4WKGDNF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 超吸引 被褥吸尘器 白色 IC-FAC2</t>
+          <t>HAUSHOF 被褥吸尘器 被褥吸尘器 螨虫 吸尘器 防螨 UV除菌 无线 60000次/分钟高速敲打 HEPA过滤网 被褥 床 沙发 地毯 靠垫 毛/垃圾/除尘 1.4kg轻量化</t>
         </is>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B01GUPMJMA?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0F4WKGDNF?psc=1</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31aFWaIaVDL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61eXaPVVpIL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>B01GUPMJMA</t>
+          <t>B0F4WKGDNF</t>
         </is>
       </c>
       <c r="M26" s="12" t="inlineStr">
@@ -13329,13 +13053,13 @@
         </is>
       </c>
       <c r="O26" s="13">
-        <v>50191</v>
+        <v>134942</v>
       </c>
       <c r="P26" s="13">
-        <v>-160820</v>
+        <v>-62285</v>
       </c>
       <c r="Q26" s="14">
-        <v>-3.34</v>
+        <v>-0.86</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -13344,17 +13068,17 @@
       </c>
       <c r="S26" s="16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T26" s="13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="U26" s="14">
-        <v>0.07</v>
+        <v>0.23</v>
       </c>
       <c r="V26" s="13">
-        <v>236740</v>
+        <v>227400</v>
       </c>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
@@ -13362,39 +13086,37 @@
         <v>1</v>
       </c>
       <c r="Z26" s="13">
-        <v>8455</v>
+        <v>7580</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
-      <c r="AC26" s="13">
-        <v>81</v>
-      </c>
+      <c r="AC26" s="13"/>
       <c r="AD26" s="17">
-        <v>1902</v>
+        <v>13</v>
       </c>
       <c r="AE26" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="18">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG26" s="19">
-        <v>0.10710000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="13">
-        <v>675</v>
+        <v>472</v>
       </c>
       <c r="AI26" s="14">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AJ26"/>
       <c r="AK26" s="11" t="inlineStr">
         <is>
-          <t>2016-06-11</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AL26" s="17">
-        <v>3770</v>
+        <v>511</v>
       </c>
       <c r="AM26" s="11" t="inlineStr">
         <is>
@@ -13405,14 +13127,14 @@
       <c r="AO26" s="11"/>
       <c r="AP26"/>
       <c r="AQ26" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR26" s="17">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AS26" s="12" t="inlineStr">
         <is>
-          <t>FASネット部門(古物商許可、インボイス制度登録)</t>
+          <t>Megastar Store</t>
         </is>
       </c>
       <c r="AT26" s="11" t="inlineStr">
@@ -13422,29 +13144,29 @@
       </c>
       <c r="AU26" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV26" s="12" t="inlineStr">
         <is>
-          <t>相田６－９－１３－２</t>
+          <t>No.35 Jiuhuan Road, Jiubao Town,</t>
         </is>
       </c>
       <c r="AW26" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR8B5CKEPZWTA</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES</t>
         </is>
       </c>
       <c r="AX26" s="11"/>
-      <c r="AY26" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY26" s="11"/>
       <c r="AZ26" s="11"/>
       <c r="BA26" s="11"/>
       <c r="BB26" s="11"/>
-      <c r="BC26" s="11"/>
+      <c r="BC26" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD26" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13454,50 +13176,46 @@
       <c r="BF26" s="11"/>
       <c r="BG26" s="11"/>
       <c r="BH26" s="12"/>
-      <c r="BI26" s="20" t="inlineStr">
-        <is>
-          <t>ic-fac2</t>
-        </is>
-      </c>
+      <c r="BI26" s="20"/>
       <c r="BJ26" s="20" t="inlineStr">
         <is>
-          <t>1.6 Kilograms</t>
+          <t>2.04 Kilograms</t>
         </is>
       </c>
       <c r="BK26" s="20" t="inlineStr">
         <is>
-          <t>1.60 kg</t>
+          <t>2.04 kg</t>
         </is>
       </c>
       <c r="BL26" s="20" t="inlineStr">
         <is>
-          <t>45.9長さ x 25幅 x 21.2高さ cm</t>
+          <t>28.2長さ x 26.1幅 x 13.9高さ cm</t>
         </is>
       </c>
       <c r="BM26" s="20"/>
       <c r="BN26" s="20" t="inlineStr">
         <is>
-          <t>2.56 kg</t>
+          <t>2.04 kg</t>
         </is>
       </c>
       <c r="BO26" s="20" t="inlineStr">
         <is>
-          <t>2.56 kg</t>
+          <t>2.04 kg</t>
         </is>
       </c>
       <c r="BP26" s="20" t="inlineStr">
         <is>
-          <t>46.4 x 28.4 x 18.4 cm</t>
+          <t>32.8 x 28.4 x 15.4 cm</t>
         </is>
       </c>
       <c r="BQ26" s="20" t="inlineStr">
         <is>
-          <t>46.40 x 28.40 x 18.40 cm</t>
+          <t>32.80 x 28.40 x 15.40 cm</t>
         </is>
       </c>
       <c r="BR26" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -13508,40 +13226,40 @@
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>B0F4WKGDNF</t>
+          <t>B09JFPJWRW</t>
         </is>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>RAYCOP(レイコップ)</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0F4WKGDNF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B09JFPJWRW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>HAUSHOF 被褥吸尘器 被褥吸尘器 螨虫 吸尘器 防螨 UV除菌 无线 60000次/分钟高速敲打 HEPA过滤网 被褥 床 沙发 地毯 靠垫 毛/垃圾/除尘 1.4kg轻量化</t>
+          <t>Raycop 雷水杯 UV 无线 被褥清洁剂 除螨病毒 UV除菌 1.4千克 超轻 独立收纳 最长可使用120分钟 强力拍打 防螨 RAYCOP 被褥吸尘器</t>
         </is>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0F4WKGDNF?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B09JFPJWRW?psc=1</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61eXaPVVpIL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61AL6xxWioL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>B0F4WKGDNF</t>
+          <t>B09JFPJWRW</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
@@ -13555,13 +13273,13 @@
         </is>
       </c>
       <c r="O27" s="13">
-        <v>134942</v>
+        <v>175879</v>
       </c>
       <c r="P27" s="13">
-        <v>-62285</v>
+        <v>-6301</v>
       </c>
       <c r="Q27" s="14">
-        <v>-0.86</v>
+        <v>-0.04</v>
       </c>
       <c r="R27" s="15" t="inlineStr">
         <is>
@@ -13570,17 +13288,17 @@
       </c>
       <c r="S27" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T27" s="13">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="U27" s="14">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="V27" s="13">
-        <v>227400</v>
+        <v>200200</v>
       </c>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
@@ -13588,41 +13306,41 @@
         <v>1</v>
       </c>
       <c r="Z27" s="13">
-        <v>7580</v>
+        <v>18200</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="13"/>
       <c r="AD27" s="17">
-        <v>13</v>
+        <v>491</v>
       </c>
       <c r="AE27" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" s="18">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AG27" s="19">
-        <v>0</v>
+        <v>0.0909</v>
       </c>
       <c r="AH27" s="13">
-        <v>472</v>
+        <v>781</v>
       </c>
       <c r="AI27" s="14">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="AJ27"/>
       <c r="AK27" s="11" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2021-10-16</t>
         </is>
       </c>
       <c r="AL27" s="17">
-        <v>511</v>
+        <v>1817</v>
       </c>
       <c r="AM27" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN27" s="11"/>
@@ -13636,27 +13354,27 @@
       </c>
       <c r="AS27" s="12" t="inlineStr">
         <is>
-          <t>Megastar Store</t>
+          <t>トラストネット卸（すり替え防止対策店、適格請求書発行事業者）</t>
         </is>
       </c>
       <c r="AT27" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU27" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV27" s="12" t="inlineStr">
         <is>
-          <t>No.35 Jiuhuan Road, Jiubao Town,</t>
+          <t>南陽市 山形県 9992232 JP</t>
         </is>
       </c>
       <c r="AW27" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A7VAMUSDN30F</t>
         </is>
       </c>
       <c r="AX27" s="11"/>
@@ -13681,43 +13399,47 @@
       <c r="BI27" s="20"/>
       <c r="BJ27" s="20" t="inlineStr">
         <is>
-          <t>2.04 Kilograms</t>
+          <t>1.26 kg</t>
         </is>
       </c>
       <c r="BK27" s="20" t="inlineStr">
         <is>
-          <t>2.04 kg</t>
+          <t>1.26 kg</t>
         </is>
       </c>
       <c r="BL27" s="20" t="inlineStr">
         <is>
-          <t>28.2長さ x 26.1幅 x 13.9高さ cm</t>
-        </is>
-      </c>
-      <c r="BM27" s="20"/>
+          <t>25 x 61.3 x 14.2 cm</t>
+        </is>
+      </c>
+      <c r="BM27" s="20" t="inlineStr">
+        <is>
+          <t>25.00 x 61.30 x 14.20 cm</t>
+        </is>
+      </c>
       <c r="BN27" s="20" t="inlineStr">
         <is>
-          <t>2.04 kg</t>
+          <t>2.46 kg</t>
         </is>
       </c>
       <c r="BO27" s="20" t="inlineStr">
         <is>
-          <t>2.04 kg</t>
+          <t>2.46 kg</t>
         </is>
       </c>
       <c r="BP27" s="20" t="inlineStr">
         <is>
-          <t>32.8 x 28.4 x 15.4 cm</t>
+          <t>57.4 x 30.6 x 26.6 cm</t>
         </is>
       </c>
       <c r="BQ27" s="20" t="inlineStr">
         <is>
-          <t>32.80 x 28.40 x 15.40 cm</t>
+          <t>57.40 x 30.60 x 26.60 cm</t>
         </is>
       </c>
       <c r="BR27" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -13728,40 +13450,40 @@
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>B09JFPJWRW</t>
+          <t>B0CRYZV8CQ</t>
         </is>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>RAYCOP(レイコップ)</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B09JFPJWRW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/JIMMY/page/A7D1BFC6-FA2F-4840-A78D-62132A51D89B?lp_asin=B0CRYZV8CQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Raycop 雷水杯 UV 无线 被褥清洁剂 除螨病毒 UV除菌 1.4千克 超轻 独立收纳 最长可使用120分钟 强力拍打 防螨 RAYCOP 被褥吸尘器</t>
+          <t>Jimmy 被子清洁器 专用被子清洁机 螨虫清洁机 床上清洁机 螨虫灰尘传感器 被子拍打 UV除菌 16Kpa 480w超高速拍打 超吸引 60度温风功能 花粉 螨虫防治 螨虫驱除 室内灰尘 地毯 床 梅雨 (BX7 Pro)</t>
         </is>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09JFPJWRW?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CRYZV8CQ?psc=1</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61AL6xxWioL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61nCrGLFc4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>B09JFPJWRW</t>
+          <t>B0CRYZV8CQ</t>
         </is>
       </c>
       <c r="M28" s="12" t="inlineStr">
@@ -13775,13 +13497,13 @@
         </is>
       </c>
       <c r="O28" s="13">
-        <v>175879</v>
+        <v>166177</v>
       </c>
       <c r="P28" s="13">
-        <v>-6301</v>
+        <v>251</v>
       </c>
       <c r="Q28" s="14">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="R28" s="15" t="inlineStr">
         <is>
@@ -13794,13 +13516,13 @@
         </is>
       </c>
       <c r="T28" s="13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U28" s="14">
-        <v>0.16</v>
+        <v>-0.42</v>
       </c>
       <c r="V28" s="13">
-        <v>200200</v>
+        <v>174993</v>
       </c>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
@@ -13808,37 +13530,37 @@
         <v>1</v>
       </c>
       <c r="Z28" s="13">
-        <v>18200</v>
+        <v>24999</v>
       </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28" s="13"/>
       <c r="AD28" s="17">
-        <v>491</v>
+        <v>167</v>
       </c>
       <c r="AE28" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF28" s="18">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG28" s="19">
-        <v>0.0909</v>
+        <v>0.4286</v>
       </c>
       <c r="AH28" s="13">
         <v>781</v>
       </c>
       <c r="AI28" s="14">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="AJ28"/>
       <c r="AK28" s="11" t="inlineStr">
         <is>
-          <t>2021-10-16</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AL28" s="17">
-        <v>1817</v>
+        <v>998</v>
       </c>
       <c r="AM28" s="11" t="inlineStr">
         <is>
@@ -13849,14 +13571,14 @@
       <c r="AO28" s="11"/>
       <c r="AP28"/>
       <c r="AQ28" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR28" s="17">
         <v>1</v>
       </c>
       <c r="AS28" s="12" t="inlineStr">
         <is>
-          <t>トラストネット卸（すり替え防止対策店、適格請求書発行事業者）</t>
+          <t>Jimmy-JP</t>
         </is>
       </c>
       <c r="AT28" s="11" t="inlineStr">
@@ -13866,17 +13588,17 @@
       </c>
       <c r="AU28" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV28" s="12" t="inlineStr">
         <is>
-          <t>南陽市 山形県 9992232 JP</t>
+          <t>TSUEN WAN NT TSUEN WAN NT 999077 HK</t>
         </is>
       </c>
       <c r="AW28" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A7VAMUSDN30F</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A27XS3ZIJF6R09</t>
         </is>
       </c>
       <c r="AX28" s="11"/>
@@ -13901,42 +13623,38 @@
       <c r="BI28" s="20"/>
       <c r="BJ28" s="20" t="inlineStr">
         <is>
-          <t>1.26 kg</t>
+          <t>2.7 kg</t>
         </is>
       </c>
       <c r="BK28" s="20" t="inlineStr">
         <is>
-          <t>1.26 kg</t>
+          <t>2.70 kg</t>
         </is>
       </c>
       <c r="BL28" s="20" t="inlineStr">
         <is>
-          <t>25 x 61.3 x 14.2 cm</t>
-        </is>
-      </c>
-      <c r="BM28" s="20" t="inlineStr">
-        <is>
-          <t>25.00 x 61.30 x 14.20 cm</t>
-        </is>
-      </c>
+          <t>36長さ x 28幅 x 20高さ cm</t>
+        </is>
+      </c>
+      <c r="BM28" s="20"/>
       <c r="BN28" s="20" t="inlineStr">
         <is>
-          <t>2.46 kg</t>
+          <t>3.7 kg</t>
         </is>
       </c>
       <c r="BO28" s="20" t="inlineStr">
         <is>
-          <t>2.46 kg</t>
+          <t>3.70 kg</t>
         </is>
       </c>
       <c r="BP28" s="20" t="inlineStr">
         <is>
-          <t>57.4 x 30.6 x 26.6 cm</t>
+          <t>41.9 x 33.2 x 25.1 cm</t>
         </is>
       </c>
       <c r="BQ28" s="20" t="inlineStr">
         <is>
-          <t>57.40 x 30.60 x 26.60 cm</t>
+          <t>41.90 x 33.20 x 25.10 cm</t>
         </is>
       </c>
       <c r="BR28" s="11" t="inlineStr">
@@ -13952,40 +13670,40 @@
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>B0CRYZV8CQ</t>
+          <t>B082C6KRNV</t>
         </is>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>RAYCOP(レイコップ)</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/JIMMY/page/A7D1BFC6-FA2F-4840-A78D-62132A51D89B?lp_asin=B0CRYZV8CQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B082C6KRNV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Jimmy 被子清洁器 专用被子清洁机 螨虫清洁机 床上清洁机 螨虫灰尘传感器 被子拍打 UV除菌 16Kpa 480w超高速拍打 超吸引 60度温风功能 花粉 螨虫防治 螨虫驱除 室内灰尘 地毯 床 梅雨 (BX7 Pro)</t>
+          <t>RAYCOP RAYCOP 搭载温风功能 UV 被褥清洁剂 RAYCOP 专业 白色 RS3-100JPWH 拍打 28,800次 UV除菌 除病毒 通过温风消灭螨 梅雨季节对策 被褥吸尘器</t>
         </is>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CRYZV8CQ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B082C6KRNV?psc=1</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61nCrGLFc4L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71UnzlAVhEL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>B0CRYZV8CQ</t>
+          <t>B082C6KRNV</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
@@ -13999,13 +13717,13 @@
         </is>
       </c>
       <c r="O29" s="13">
-        <v>166177</v>
+        <v>292120</v>
       </c>
       <c r="P29" s="13">
-        <v>251</v>
+        <v>-151699</v>
       </c>
       <c r="Q29" s="14">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="R29" s="15" t="inlineStr">
         <is>
@@ -14014,17 +13732,17 @@
       </c>
       <c r="S29" s="16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>64</t>
         </is>
       </c>
       <c r="T29" s="13">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U29" s="14">
-        <v>-0.42</v>
+        <v>0.38</v>
       </c>
       <c r="V29" s="13">
-        <v>174993</v>
+        <v>174720</v>
       </c>
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
@@ -14032,37 +13750,39 @@
         <v>1</v>
       </c>
       <c r="Z29" s="13">
-        <v>24999</v>
+        <v>12480</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
-      <c r="AC29" s="13"/>
+      <c r="AC29" s="13">
+        <v>5</v>
+      </c>
       <c r="AD29" s="17">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="AE29" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF29" s="18">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AG29" s="19">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="AH29" s="13">
         <v>781</v>
       </c>
       <c r="AI29" s="14">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="11" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2019-12-06</t>
         </is>
       </c>
       <c r="AL29" s="17">
-        <v>998</v>
+        <v>2497</v>
       </c>
       <c r="AM29" s="11" t="inlineStr">
         <is>
@@ -14073,14 +13793,14 @@
       <c r="AO29" s="11"/>
       <c r="AP29"/>
       <c r="AQ29" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR29" s="17">
         <v>1</v>
       </c>
       <c r="AS29" s="12" t="inlineStr">
         <is>
-          <t>Jimmy-JP</t>
+          <t>ネロビア</t>
         </is>
       </c>
       <c r="AT29" s="11" t="inlineStr">
@@ -14090,17 +13810,17 @@
       </c>
       <c r="AU29" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV29" s="12" t="inlineStr">
         <is>
-          <t>TSUEN WAN NT TSUEN WAN NT 999077 HK</t>
+          <t>彦根市 滋賀県 5220029 JP</t>
         </is>
       </c>
       <c r="AW29" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A27XS3ZIJF6R09</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1J3C8YFTAUF75</t>
         </is>
       </c>
       <c r="AX29" s="11"/>
@@ -14125,38 +13845,42 @@
       <c r="BI29" s="20"/>
       <c r="BJ29" s="20" t="inlineStr">
         <is>
-          <t>2.7 kg</t>
+          <t>2.09 kg</t>
         </is>
       </c>
       <c r="BK29" s="20" t="inlineStr">
         <is>
-          <t>2.70 kg</t>
+          <t>2.09 kg</t>
         </is>
       </c>
       <c r="BL29" s="20" t="inlineStr">
         <is>
-          <t>36長さ x 28幅 x 20高さ cm</t>
-        </is>
-      </c>
-      <c r="BM29" s="20"/>
+          <t>37.4 x 31.6 x 17.2 cm</t>
+        </is>
+      </c>
+      <c r="BM29" s="20" t="inlineStr">
+        <is>
+          <t>37.40 x 31.60 x 17.20 cm</t>
+        </is>
+      </c>
       <c r="BN29" s="20" t="inlineStr">
         <is>
-          <t>3.7 kg</t>
+          <t>3.86 kg</t>
         </is>
       </c>
       <c r="BO29" s="20" t="inlineStr">
         <is>
-          <t>3.70 kg</t>
+          <t>3.86 kg</t>
         </is>
       </c>
       <c r="BP29" s="20" t="inlineStr">
         <is>
-          <t>41.9 x 33.2 x 25.1 cm</t>
+          <t>44.2 x 36.8 x 21.2 cm</t>
         </is>
       </c>
       <c r="BQ29" s="20" t="inlineStr">
         <is>
-          <t>41.90 x 33.20 x 25.10 cm</t>
+          <t>44.20 x 36.80 x 21.20 cm</t>
         </is>
       </c>
       <c r="BR29" s="11" t="inlineStr">
@@ -14172,7 +13896,7 @@
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>B082C6KRNV</t>
+          <t>B08XM26HKK</t>
         </is>
       </c>
       <c r="D30" s="12"/>
@@ -14184,28 +13908,28 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B082C6KRNV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B08XM26HKK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>RAYCOP RAYCOP 搭载温风功能 UV 被褥清洁剂 RAYCOP 专业 白色 RS3-100JPWH 拍打 28,800次 UV除菌 除病毒 通过温风消灭螨 梅雨季节对策 被褥吸尘器</t>
+          <t>Raycop 被子清洁剂 UV除菌 吸力 强力拍打 搭载光清洁机制" 病毒/室内灰尘 轻量 小巧 RE-100JWH-E 白色</t>
         </is>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B082C6KRNV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B08XM26HKK?psc=1</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71UnzlAVhEL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71ZUcvmHC5L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>B082C6KRNV</t>
+          <t>B08XM26HKK</t>
         </is>
       </c>
       <c r="M30" s="12" t="inlineStr">
@@ -14219,13 +13943,13 @@
         </is>
       </c>
       <c r="O30" s="13">
-        <v>292120</v>
+        <v>179653</v>
       </c>
       <c r="P30" s="13">
-        <v>-151699</v>
+        <v>-79773</v>
       </c>
       <c r="Q30" s="14">
-        <v>-1.08</v>
+        <v>-0.8</v>
       </c>
       <c r="R30" s="15" t="inlineStr">
         <is>
@@ -14234,17 +13958,15 @@
       </c>
       <c r="S30" s="16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T30" s="13">
-        <v>14</v>
-      </c>
-      <c r="U30" s="14">
-        <v>0.38</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="U30" s="14"/>
       <c r="V30" s="13">
-        <v>174720</v>
+        <v>170104</v>
       </c>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
@@ -14252,39 +13974,37 @@
         <v>1</v>
       </c>
       <c r="Z30" s="13">
-        <v>12480</v>
+        <v>7732</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
-      <c r="AC30" s="13">
-        <v>5</v>
-      </c>
+      <c r="AC30" s="13"/>
       <c r="AD30" s="17">
-        <v>214</v>
+        <v>326</v>
       </c>
       <c r="AE30" s="13">
         <v>0</v>
       </c>
       <c r="AF30" s="18">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG30" s="19">
         <v>0</v>
       </c>
       <c r="AH30" s="13">
-        <v>781</v>
+        <v>532</v>
       </c>
       <c r="AI30" s="14">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AJ30"/>
       <c r="AK30" s="11" t="inlineStr">
         <is>
-          <t>2019-12-06</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="AL30" s="17">
-        <v>2497</v>
+        <v>2049</v>
       </c>
       <c r="AM30" s="11" t="inlineStr">
         <is>
@@ -14302,7 +14022,7 @@
       </c>
       <c r="AS30" s="12" t="inlineStr">
         <is>
-          <t>ネロビア</t>
+          <t>モリハウス</t>
         </is>
       </c>
       <c r="AT30" s="11" t="inlineStr">
@@ -14317,12 +14037,12 @@
       </c>
       <c r="AV30" s="12" t="inlineStr">
         <is>
-          <t>彦根市 滋賀県 5220029 JP</t>
+          <t>守口市竹町 大阪府 5700086 JP</t>
         </is>
       </c>
       <c r="AW30" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1J3C8YFTAUF75</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS</t>
         </is>
       </c>
       <c r="AX30" s="11"/>
@@ -14347,47 +14067,47 @@
       <c r="BI30" s="20"/>
       <c r="BJ30" s="20" t="inlineStr">
         <is>
-          <t>2.09 kg</t>
+          <t>1.95 kg</t>
         </is>
       </c>
       <c r="BK30" s="20" t="inlineStr">
         <is>
-          <t>2.09 kg</t>
+          <t>1.95 kg</t>
         </is>
       </c>
       <c r="BL30" s="20" t="inlineStr">
         <is>
-          <t>37.4 x 31.6 x 17.2 cm</t>
+          <t>35.2 x 30 x 15.1 cm</t>
         </is>
       </c>
       <c r="BM30" s="20" t="inlineStr">
         <is>
-          <t>37.40 x 31.60 x 17.20 cm</t>
+          <t>35.20 x 30.00 x 15.10 cm</t>
         </is>
       </c>
       <c r="BN30" s="20" t="inlineStr">
         <is>
-          <t>3.86 kg</t>
+          <t>2.97 kg</t>
         </is>
       </c>
       <c r="BO30" s="20" t="inlineStr">
         <is>
-          <t>3.86 kg</t>
+          <t>2.97 kg</t>
         </is>
       </c>
       <c r="BP30" s="20" t="inlineStr">
         <is>
-          <t>44.2 x 36.8 x 21.2 cm</t>
+          <t>38.9 x 34.2 x 19.2 cm</t>
         </is>
       </c>
       <c r="BQ30" s="20" t="inlineStr">
         <is>
-          <t>44.20 x 36.80 x 21.20 cm</t>
+          <t>38.90 x 34.20 x 19.20 cm</t>
         </is>
       </c>
       <c r="BR30" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -14398,40 +14118,40 @@
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>B08XM26HKK</t>
+          <t>B0GSD3NSJC</t>
         </is>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>RAYCOP(レイコップ)</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B08XM26HKK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%EF%BC%B2%EF%BD%81%EF%BD%99%EF%BD%9A%EF%BD%8F%EF%BD%8E%EF%BD%89%EF%BD%83/page/2A2F6C67-919B-4259-BF3B-3B614F5CF4A6?lp_asin=B0GSD3NSJC&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Raycop 被子清洁剂 UV除菌 吸力 强力拍打 搭载光清洁机制" 病毒/室内灰尘 轻量 小巧 RE-100JWH-E 白色</t>
+          <t>JIGOO 被褥吸尘器 J200 带暖风 13KPa 吸引力 防紫外线 除菌 高速打 搭载HEPA 过滤器s带温风功能的被褥吸尘器 每秒200次高速拍打 0.3μm 微粒 99.9% 捕集 螨虫 毛发去除灰尘 UV 除菌功能 适合有宠物和宝宝的家</t>
         </is>
       </c>
       <c r="I31" s="12"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B08XM26HKK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GSD3NSJC?psc=1</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71ZUcvmHC5L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61lGa5v8mML._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>B08XM26HKK</t>
+          <t>B0GSD3NSJC</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
@@ -14445,13 +14165,13 @@
         </is>
       </c>
       <c r="O31" s="13">
-        <v>179653</v>
+        <v>185275</v>
       </c>
       <c r="P31" s="13">
-        <v>-79773</v>
+        <v>84587</v>
       </c>
       <c r="Q31" s="14">
-        <v>-0.8</v>
+        <v>0.31</v>
       </c>
       <c r="R31" s="15" t="inlineStr">
         <is>
@@ -14460,35 +14180,37 @@
       </c>
       <c r="S31" s="16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="T31" s="13">
-        <v>22</v>
-      </c>
-      <c r="U31" s="14"/>
+        <v>8</v>
+      </c>
+      <c r="U31" s="14">
+        <v>0</v>
+      </c>
       <c r="V31" s="13">
-        <v>170104</v>
+        <v>159840</v>
       </c>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z31" s="13">
-        <v>7732</v>
+        <v>19980</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="13"/>
       <c r="AD31" s="17">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="AE31" s="13">
         <v>0</v>
       </c>
       <c r="AF31" s="18">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG31" s="19">
         <v>0</v>
@@ -14497,39 +14219,39 @@
         <v>532</v>
       </c>
       <c r="AI31" s="14">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="11" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AL31" s="17">
-        <v>2049</v>
+        <v>190</v>
       </c>
       <c r="AM31" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN31" s="11"/>
       <c r="AO31" s="11"/>
       <c r="AP31"/>
       <c r="AQ31" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR31" s="17">
         <v>1</v>
       </c>
       <c r="AS31" s="12" t="inlineStr">
         <is>
-          <t>モリハウス</t>
+          <t>天興株式会社-JP</t>
         </is>
       </c>
       <c r="AT31" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU31" s="11" t="inlineStr">
@@ -14539,12 +14261,12 @@
       </c>
       <c r="AV31" s="12" t="inlineStr">
         <is>
-          <t>守口市竹町 大阪府 5700086 JP</t>
+          <t>大阪市 大阪府 5450023 JP</t>
         </is>
       </c>
       <c r="AW31" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23HRKZCC74EMZ</t>
         </is>
       </c>
       <c r="AX31" s="11"/>
@@ -14569,42 +14291,38 @@
       <c r="BI31" s="20"/>
       <c r="BJ31" s="20" t="inlineStr">
         <is>
-          <t>1.95 kg</t>
+          <t>2.28 Kilograms</t>
         </is>
       </c>
       <c r="BK31" s="20" t="inlineStr">
         <is>
-          <t>1.95 kg</t>
+          <t>2.28 kg</t>
         </is>
       </c>
       <c r="BL31" s="20" t="inlineStr">
         <is>
-          <t>35.2 x 30 x 15.1 cm</t>
-        </is>
-      </c>
-      <c r="BM31" s="20" t="inlineStr">
-        <is>
-          <t>35.20 x 30.00 x 15.10 cm</t>
-        </is>
-      </c>
+          <t>27長さ x 25幅 x 34高さ cm</t>
+        </is>
+      </c>
+      <c r="BM31" s="20"/>
       <c r="BN31" s="20" t="inlineStr">
         <is>
-          <t>2.97 kg</t>
+          <t>2.28 kg</t>
         </is>
       </c>
       <c r="BO31" s="20" t="inlineStr">
         <is>
-          <t>2.97 kg</t>
+          <t>2.28 kg</t>
         </is>
       </c>
       <c r="BP31" s="20" t="inlineStr">
         <is>
-          <t>38.9 x 34.2 x 19.2 cm</t>
+          <t>35 x 28.6 x 19.2 cm</t>
         </is>
       </c>
       <c r="BQ31" s="20" t="inlineStr">
         <is>
-          <t>38.90 x 34.20 x 19.20 cm</t>
+          <t>35.00 x 28.60 x 19.20 cm</t>
         </is>
       </c>
       <c r="BR31" s="11" t="inlineStr">
@@ -14620,40 +14338,40 @@
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>B0GSD3NSJC</t>
+          <t>B0BCF1JPCL</t>
         </is>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%EF%BC%B2%EF%BD%81%EF%BD%99%EF%BD%9A%EF%BD%8F%EF%BD%8E%EF%BD%89%EF%BD%83/page/2A2F6C67-919B-4259-BF3B-3B614F5CF4A6?lp_asin=B0GSD3NSJC&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BCF1JPCL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>JIGOO 被褥吸尘器 J200 带暖风 13KPa 吸引力 防紫外线 除菌 高速打 搭载HEPA 过滤器s带温风功能的被褥吸尘器 每秒200次高速拍打 0.3μm 微粒 99.9% 捕集 螨虫 毛发去除灰尘 UV 除菌功能 适合有宠物和宝宝的家</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 被褥吸尘器 拍打次数 每分钟7000次 搭载螨虫检测传感器 白色 FCA-A</t>
         </is>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GSD3NSJC?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0BCF1JPCL?psc=1</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61lGa5v8mML._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/41AW0SKsHqL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>B0GSD3NSJC</t>
+          <t>B0BCF1JPCL</t>
         </is>
       </c>
       <c r="M32" s="12" t="inlineStr">
@@ -14667,13 +14385,13 @@
         </is>
       </c>
       <c r="O32" s="13">
-        <v>185275</v>
+        <v>62559</v>
       </c>
       <c r="P32" s="13">
-        <v>84587</v>
+        <v>204956</v>
       </c>
       <c r="Q32" s="14">
-        <v>0.31</v>
+        <v>0.77</v>
       </c>
       <c r="R32" s="15" t="inlineStr">
         <is>
@@ -14682,59 +14400,59 @@
       </c>
       <c r="S32" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T32" s="13">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U32" s="14">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="V32" s="13">
-        <v>159840</v>
+        <v>151680</v>
       </c>
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="13">
-        <v>19980</v>
+        <v>9798</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="13"/>
       <c r="AD32" s="17">
-        <v>363</v>
+        <v>5</v>
       </c>
       <c r="AE32" s="13">
         <v>0</v>
       </c>
       <c r="AF32" s="18">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AG32" s="19">
         <v>0</v>
       </c>
       <c r="AH32" s="13">
-        <v>532</v>
+        <v>675</v>
       </c>
       <c r="AI32" s="14">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AL32" s="17">
-        <v>190</v>
+        <v>1489</v>
       </c>
       <c r="AM32" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN32" s="11"/>
@@ -14744,16 +14462,16 @@
         <v>9</v>
       </c>
       <c r="AR32" s="17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AS32" s="12" t="inlineStr">
         <is>
-          <t>天興株式会社-JP</t>
+          <t>合同会社レステリオ</t>
         </is>
       </c>
       <c r="AT32" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU32" s="11" t="inlineStr">
@@ -14763,12 +14481,12 @@
       </c>
       <c r="AV32" s="12" t="inlineStr">
         <is>
-          <t>大阪市 大阪府 5450023 JP</t>
+          <t>八王子市 東京都 1930812 JP</t>
         </is>
       </c>
       <c r="AW32" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23HRKZCC74EMZ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17TIQMTOKKTIR</t>
         </is>
       </c>
       <c r="AX32" s="11"/>
@@ -14781,11 +14499,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD32" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD32" s="11"/>
       <c r="BE32" s="11"/>
       <c r="BF32" s="11"/>
       <c r="BG32" s="11"/>
@@ -14793,43 +14507,47 @@
       <c r="BI32" s="20"/>
       <c r="BJ32" s="20" t="inlineStr">
         <is>
-          <t>2.28 Kilograms</t>
+          <t>1.6 kg</t>
         </is>
       </c>
       <c r="BK32" s="20" t="inlineStr">
         <is>
-          <t>2.28 kg</t>
+          <t>1.60 kg</t>
         </is>
       </c>
       <c r="BL32" s="20" t="inlineStr">
         <is>
-          <t>27長さ x 25幅 x 34高さ cm</t>
-        </is>
-      </c>
-      <c r="BM32" s="20"/>
+          <t>46.6 x 28.4 x 18.6 cm</t>
+        </is>
+      </c>
+      <c r="BM32" s="20" t="inlineStr">
+        <is>
+          <t>46.60 x 28.40 x 18.60 cm</t>
+        </is>
+      </c>
       <c r="BN32" s="20" t="inlineStr">
         <is>
-          <t>2.28 kg</t>
+          <t>2.57 kg</t>
         </is>
       </c>
       <c r="BO32" s="20" t="inlineStr">
         <is>
-          <t>2.28 kg</t>
+          <t>2.57 kg</t>
         </is>
       </c>
       <c r="BP32" s="20" t="inlineStr">
         <is>
-          <t>35 x 28.6 x 19.2 cm</t>
+          <t>46.6 x 28.4 x 18.6 cm</t>
         </is>
       </c>
       <c r="BQ32" s="20" t="inlineStr">
         <is>
-          <t>35.00 x 28.60 x 19.20 cm</t>
+          <t>46.60 x 28.40 x 18.60 cm</t>
         </is>
       </c>
       <c r="BR32" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -14840,40 +14558,40 @@
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>B0BCF1JPCL</t>
+          <t>B017SAF6OY</t>
         </is>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
+          <t>IWA</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BCF1JPCL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/IWA/b/ref=bl_dp_s_web_3622059051?ie=UTF8&amp;node=3622059051&amp;field-lbr_brands_browse-bin=IWA</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 被褥吸尘器 拍打次数 每分钟7000次 搭载螨虫检测传感器 白色 FCA-A</t>
+          <t>Aiwa 花粉・螨虫去除 被褥专用喷嘴 花粉&amp;螨虫清洁器 日本制造</t>
         </is>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0BCF1JPCL?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B017SAF6OY?psc=1</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41AW0SKsHqL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31fosM0+zwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>B0BCF1JPCL</t>
+          <t>B017SAF6OY</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
@@ -14887,13 +14605,13 @@
         </is>
       </c>
       <c r="O33" s="13">
-        <v>62559</v>
+        <v>45218</v>
       </c>
       <c r="P33" s="13">
-        <v>204956</v>
+        <v>-8787</v>
       </c>
       <c r="Q33" s="14">
-        <v>0.77</v>
+        <v>-0.24</v>
       </c>
       <c r="R33" s="15" t="inlineStr">
         <is>
@@ -14902,95 +14620,91 @@
       </c>
       <c r="S33" s="16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T33" s="13">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="U33" s="14">
-        <v>-0.38</v>
+        <v>0.11</v>
       </c>
       <c r="V33" s="13">
-        <v>151680</v>
-      </c>
-      <c r="W33" s="13"/>
-      <c r="X33" s="13"/>
+        <v>140530</v>
+      </c>
+      <c r="W33" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X33" s="13">
+        <v>82250</v>
+      </c>
       <c r="Y33" s="17">
         <v>1</v>
       </c>
       <c r="Z33" s="13">
-        <v>9798</v>
+        <v>10</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
-      <c r="AC33" s="13"/>
+      <c r="AC33" s="13">
+        <v>10</v>
+      </c>
       <c r="AD33" s="17">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="AE33" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF33" s="18">
         <v>3.7</v>
       </c>
       <c r="AG33" s="19">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="AH33" s="13">
-        <v>675</v>
+        <v>430</v>
       </c>
       <c r="AI33" s="14">
-        <v>0.78</v>
+        <v>0.59</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="11" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
+          <t>2016-02-09</t>
         </is>
       </c>
       <c r="AL33" s="17">
-        <v>1489</v>
+        <v>3894</v>
       </c>
       <c r="AM33" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN33" s="11"/>
       <c r="AO33" s="11"/>
       <c r="AP33"/>
       <c r="AQ33" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR33" s="17">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AS33" s="12" t="inlineStr">
         <is>
-          <t>合同会社レステリオ</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT33" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU33" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV33" s="12" t="inlineStr">
-        <is>
-          <t>八王子市 東京都 1930812 JP</t>
-        </is>
-      </c>
-      <c r="AW33" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17TIQMTOKKTIR</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU33" s="11"/>
+      <c r="AV33" s="12"/>
+      <c r="AW33" s="11"/>
       <c r="AX33" s="11"/>
       <c r="AY33" s="11"/>
       <c r="AZ33" s="11"/>
@@ -15009,47 +14723,47 @@
       <c r="BI33" s="20"/>
       <c r="BJ33" s="20" t="inlineStr">
         <is>
-          <t>1.6 kg</t>
+          <t>240 g</t>
         </is>
       </c>
       <c r="BK33" s="20" t="inlineStr">
         <is>
-          <t>1.60 kg</t>
+          <t>240.00 g</t>
         </is>
       </c>
       <c r="BL33" s="20" t="inlineStr">
         <is>
-          <t>46.6 x 28.4 x 18.6 cm</t>
+          <t>31.5 x 20.2 x 5.9 cm</t>
         </is>
       </c>
       <c r="BM33" s="20" t="inlineStr">
         <is>
-          <t>46.60 x 28.40 x 18.60 cm</t>
+          <t>31.50 x 20.20 x 5.90 cm</t>
         </is>
       </c>
       <c r="BN33" s="20" t="inlineStr">
         <is>
-          <t>2.57 kg</t>
+          <t>380 g</t>
         </is>
       </c>
       <c r="BO33" s="20" t="inlineStr">
         <is>
-          <t>2.57 kg</t>
+          <t>380.00 g</t>
         </is>
       </c>
       <c r="BP33" s="20" t="inlineStr">
         <is>
-          <t>46.6 x 28.4 x 18.6 cm</t>
+          <t>31.5 x 20.2 x 5.9 cm</t>
         </is>
       </c>
       <c r="BQ33" s="20" t="inlineStr">
         <is>
-          <t>46.60 x 28.40 x 18.60 cm</t>
+          <t>31.50 x 20.20 x 5.90 cm</t>
         </is>
       </c>
       <c r="BR33" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -15060,40 +14774,40 @@
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>B017SAF6OY</t>
+          <t>B0DQSGMXJB</t>
         </is>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>IWA</t>
+          <t>FEVORCS</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/IWA/b/ref=bl_dp_s_web_3622059051?ie=UTF8&amp;node=3622059051&amp;field-lbr_brands_browse-bin=IWA</t>
+          <t>https://www.amazon.co.jp/stores/FEVORCS/page/2392B65D-91DF-4046-9C5C-89C6E6899285?lp_asin=B0DQSGMXJB&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Aiwa 花粉・螨虫去除 被褥专用喷嘴 花粉&amp;螨虫清洁器 日本制造</t>
+          <t>FEVORCS 被褥吸尘器 5M线 被褥清洁器</t>
         </is>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B017SAF6OY?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DQSGMXJB?psc=1</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31fosM0+zwL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/616rv7jIiuL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>B017SAF6OY</t>
+          <t>B0DQSGMXJB</t>
         </is>
       </c>
       <c r="M34" s="12" t="inlineStr">
@@ -15107,13 +14821,13 @@
         </is>
       </c>
       <c r="O34" s="13">
-        <v>45218</v>
+        <v>164467</v>
       </c>
       <c r="P34" s="13">
-        <v>-8787</v>
+        <v>86855</v>
       </c>
       <c r="Q34" s="14">
-        <v>-0.24</v>
+        <v>0.35</v>
       </c>
       <c r="R34" s="15" t="inlineStr">
         <is>
@@ -15122,91 +14836,95 @@
       </c>
       <c r="S34" s="16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T34" s="13">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="U34" s="14">
-        <v>0.11</v>
+        <v>-0.44</v>
       </c>
       <c r="V34" s="13">
-        <v>140530</v>
-      </c>
-      <c r="W34" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X34" s="13">
-        <v>82250</v>
-      </c>
+        <v>127400</v>
+      </c>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
       <c r="Y34" s="17">
         <v>1</v>
       </c>
       <c r="Z34" s="13">
-        <v>10</v>
+        <v>9800</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
-      <c r="AC34" s="13">
-        <v>10</v>
-      </c>
+      <c r="AC34" s="13"/>
       <c r="AD34" s="17">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="AE34" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF34" s="18">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="AG34" s="19">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="AH34" s="13">
-        <v>430</v>
+        <v>675</v>
       </c>
       <c r="AI34" s="14">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="11" t="inlineStr">
         <is>
-          <t>2016-02-09</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="AL34" s="17">
-        <v>3894</v>
+        <v>635</v>
       </c>
       <c r="AM34" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN34" s="11"/>
       <c r="AO34" s="11"/>
       <c r="AP34"/>
       <c r="AQ34" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR34" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS34" s="12" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Koda Electrical</t>
         </is>
       </c>
       <c r="AT34" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU34" s="11"/>
-      <c r="AV34" s="12"/>
-      <c r="AW34" s="11"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU34" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV34" s="12" t="inlineStr">
+        <is>
+          <t>苏州市 江苏省 215128 CN</t>
+        </is>
+      </c>
+      <c r="AW34" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A130FCCM5YKTQ1</t>
+        </is>
+      </c>
       <c r="AX34" s="11"/>
       <c r="AY34" s="11"/>
       <c r="AZ34" s="11"/>
@@ -15225,47 +14943,43 @@
       <c r="BI34" s="20"/>
       <c r="BJ34" s="20" t="inlineStr">
         <is>
-          <t>240 g</t>
+          <t>2.81 Kilograms</t>
         </is>
       </c>
       <c r="BK34" s="20" t="inlineStr">
         <is>
-          <t>240.00 g</t>
+          <t>2.81 kg</t>
         </is>
       </c>
       <c r="BL34" s="20" t="inlineStr">
         <is>
-          <t>31.5 x 20.2 x 5.9 cm</t>
-        </is>
-      </c>
-      <c r="BM34" s="20" t="inlineStr">
-        <is>
-          <t>31.50 x 20.20 x 5.90 cm</t>
-        </is>
-      </c>
+          <t>33長さ x 26.9幅 x 20.3高さ cm</t>
+        </is>
+      </c>
+      <c r="BM34" s="20"/>
       <c r="BN34" s="20" t="inlineStr">
         <is>
-          <t>380 g</t>
+          <t>2.81 kg</t>
         </is>
       </c>
       <c r="BO34" s="20" t="inlineStr">
         <is>
-          <t>380.00 g</t>
+          <t>2.81 kg</t>
         </is>
       </c>
       <c r="BP34" s="20" t="inlineStr">
         <is>
-          <t>31.5 x 20.2 x 5.9 cm</t>
+          <t>37.4 x 28.7 x 25.1 cm</t>
         </is>
       </c>
       <c r="BQ34" s="20" t="inlineStr">
         <is>
-          <t>31.50 x 20.20 x 5.90 cm</t>
+          <t>37.40 x 28.70 x 25.10 cm</t>
         </is>
       </c>
       <c r="BR34" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -15276,40 +14990,40 @@
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>B0DQSGMXJB</t>
+          <t>B0DGTN1LGP</t>
         </is>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>FEVORCS</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/FEVORCS/page/2392B65D-91DF-4046-9C5C-89C6E6899285?lp_asin=B0DQSGMXJB&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jp/stores/JIMMY/page/A7D1BFC6-FA2F-4840-A78D-62132A51D89B?lp_asin=B0DGTN1LGP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>FEVORCS 被褥吸尘器 5M线 被褥清洁器</t>
+          <t>Jimmy 被子清洁器 被子用吸尘器 螨虫清除吸尘器 床上清洁器 螨虫灰尘传感器 被子拍打 UV消毒 15Kpa 500w超高速拍打 超吸力 65度温风功能 花粉 螨虫防护 螨虫驱除 室内灰尘 地毯 床 梅雨（WB81）</t>
         </is>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DQSGMXJB?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DGTN1LGP?psc=1</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/616rv7jIiuL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61q8jT7-5rL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>B0DQSGMXJB</t>
+          <t>B0DGTN1LGP</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
@@ -15323,13 +15037,13 @@
         </is>
       </c>
       <c r="O35" s="13">
-        <v>164467</v>
+        <v>205665</v>
       </c>
       <c r="P35" s="13">
-        <v>86855</v>
+        <v>-6817</v>
       </c>
       <c r="Q35" s="14">
-        <v>0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="R35" s="15" t="inlineStr">
         <is>
@@ -15338,17 +15052,17 @@
       </c>
       <c r="S35" s="16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T35" s="13">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U35" s="14">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="V35" s="13">
-        <v>127400</v>
+        <v>99995</v>
       </c>
       <c r="W35" s="13"/>
       <c r="X35" s="13"/>
@@ -15356,75 +15070,75 @@
         <v>1</v>
       </c>
       <c r="Z35" s="13">
-        <v>9800</v>
+        <v>19999</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="13"/>
       <c r="AD35" s="17">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="AE35" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF35" s="18">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AG35" s="19">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH35" s="13">
-        <v>675</v>
+        <v>781</v>
       </c>
       <c r="AI35" s="14">
-        <v>0.78</v>
+        <v>0.81</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="11" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AL35" s="17">
-        <v>635</v>
+        <v>753</v>
       </c>
       <c r="AM35" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN35" s="11"/>
       <c r="AO35" s="11"/>
       <c r="AP35"/>
       <c r="AQ35" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR35" s="17">
         <v>1</v>
       </c>
       <c r="AS35" s="12" t="inlineStr">
         <is>
-          <t>Koda Electrical</t>
+          <t>Jimmy-JP</t>
         </is>
       </c>
       <c r="AT35" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU35" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV35" s="12" t="inlineStr">
         <is>
-          <t>苏州市 江苏省 215128 CN</t>
+          <t>TSUEN WAN NT TSUEN WAN NT 999077 HK</t>
         </is>
       </c>
       <c r="AW35" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A130FCCM5YKTQ1</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A27XS3ZIJF6R09</t>
         </is>
       </c>
       <c r="AX35" s="11"/>
@@ -15437,7 +15151,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD35" s="11"/>
+      <c r="BD35" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE35" s="11"/>
       <c r="BF35" s="11"/>
       <c r="BG35" s="11"/>
@@ -15445,38 +15163,38 @@
       <c r="BI35" s="20"/>
       <c r="BJ35" s="20" t="inlineStr">
         <is>
-          <t>2.81 Kilograms</t>
+          <t>2 kg</t>
         </is>
       </c>
       <c r="BK35" s="20" t="inlineStr">
         <is>
-          <t>2.81 kg</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BL35" s="20" t="inlineStr">
         <is>
-          <t>33長さ x 26.9幅 x 20.3高さ cm</t>
+          <t>33長さ x 20幅 x 28高さ cm</t>
         </is>
       </c>
       <c r="BM35" s="20"/>
       <c r="BN35" s="20" t="inlineStr">
         <is>
-          <t>2.81 kg</t>
+          <t>3.77 kg</t>
         </is>
       </c>
       <c r="BO35" s="20" t="inlineStr">
         <is>
-          <t>2.81 kg</t>
+          <t>3.77 kg</t>
         </is>
       </c>
       <c r="BP35" s="20" t="inlineStr">
         <is>
-          <t>37.4 x 28.7 x 25.1 cm</t>
+          <t>45.5 x 37.2 x 27.5 cm</t>
         </is>
       </c>
       <c r="BQ35" s="20" t="inlineStr">
         <is>
-          <t>37.40 x 28.70 x 25.10 cm</t>
+          <t>45.50 x 37.20 x 27.50 cm</t>
         </is>
       </c>
       <c r="BR35" s="11" t="inlineStr">
@@ -15492,40 +15210,40 @@
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>B0DGTN1LGP</t>
+          <t>B087Z4YF8S</t>
         </is>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/JIMMY/page/A7D1BFC6-FA2F-4840-A78D-62132A51D89B?lp_asin=B0DGTN1LGP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B087Z4YF8S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Jimmy 被子清洁器 被子用吸尘器 螨虫清除吸尘器 床上清洁器 螨虫灰尘传感器 被子拍打 UV消毒 15Kpa 500w超高速拍打 超吸力 65度温风功能 花粉 螨虫防护 螨虫驱除 室内灰尘 地毯 床 梅雨（WB81）</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 被褥清洁剂 大功率模型 防螨 宽头 拍打 约14000次/分钟 IC-FAC</t>
         </is>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DGTN1LGP?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B087Z4YF8S?psc=1</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61q8jT7-5rL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51FXGYp5BcL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>B0DGTN1LGP</t>
+          <t>B087Z4YF8S</t>
         </is>
       </c>
       <c r="M36" s="12" t="inlineStr">
@@ -15539,13 +15257,13 @@
         </is>
       </c>
       <c r="O36" s="13">
-        <v>205665</v>
+        <v>164886</v>
       </c>
       <c r="P36" s="13">
-        <v>-6817</v>
+        <v>-25857</v>
       </c>
       <c r="Q36" s="14">
-        <v>-0.03</v>
+        <v>-0.19</v>
       </c>
       <c r="R36" s="15" t="inlineStr">
         <is>
@@ -15554,55 +15272,57 @@
       </c>
       <c r="S36" s="16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T36" s="13">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="U36" s="14">
-        <v>0</v>
+        <v>-0.07</v>
       </c>
       <c r="V36" s="13">
-        <v>99995</v>
+        <v>97500</v>
       </c>
       <c r="W36" s="13"/>
       <c r="X36" s="13"/>
       <c r="Y36" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z36" s="13">
-        <v>19999</v>
+        <v>21500</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
-      <c r="AC36" s="13"/>
+      <c r="AC36" s="13">
+        <v>57</v>
+      </c>
       <c r="AD36" s="17">
-        <v>57</v>
+        <v>1272</v>
       </c>
       <c r="AE36" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF36" s="18">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG36" s="19">
-        <v>0.2</v>
+        <v>0.1333</v>
       </c>
       <c r="AH36" s="13">
         <v>781</v>
       </c>
       <c r="AI36" s="14">
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="11" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AL36" s="17">
-        <v>753</v>
+        <v>2349</v>
       </c>
       <c r="AM36" s="11" t="inlineStr">
         <is>
@@ -15616,11 +15336,11 @@
         <v>10</v>
       </c>
       <c r="AR36" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS36" s="12" t="inlineStr">
         <is>
-          <t>Jimmy-JP</t>
+          <t>スケチヨ商店(適格請求書発行事業者)</t>
         </is>
       </c>
       <c r="AT36" s="11" t="inlineStr">
@@ -15630,17 +15350,17 @@
       </c>
       <c r="AU36" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV36" s="12" t="inlineStr">
         <is>
-          <t>TSUEN WAN NT TSUEN WAN NT 999077 HK</t>
+          <t>三原市 広島県 7230052 JP</t>
         </is>
       </c>
       <c r="AW36" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A27XS3ZIJF6R09</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JLEXPXXTRB24</t>
         </is>
       </c>
       <c r="AX36" s="11"/>
@@ -15665,38 +15385,42 @@
       <c r="BI36" s="20"/>
       <c r="BJ36" s="20" t="inlineStr">
         <is>
-          <t>2 kg</t>
+          <t>2.2 kg</t>
         </is>
       </c>
       <c r="BK36" s="20" t="inlineStr">
         <is>
-          <t>2.00 kg</t>
+          <t>2.20 kg</t>
         </is>
       </c>
       <c r="BL36" s="20" t="inlineStr">
         <is>
-          <t>33長さ x 20幅 x 28高さ cm</t>
-        </is>
-      </c>
-      <c r="BM36" s="20"/>
+          <t>50.1 x 30 x 21.8 cm</t>
+        </is>
+      </c>
+      <c r="BM36" s="20" t="inlineStr">
+        <is>
+          <t>50.10 x 30.00 x 21.80 cm</t>
+        </is>
+      </c>
       <c r="BN36" s="20" t="inlineStr">
         <is>
-          <t>3.77 kg</t>
+          <t>3 kg</t>
         </is>
       </c>
       <c r="BO36" s="20" t="inlineStr">
         <is>
-          <t>3.77 kg</t>
+          <t>3.00 kg</t>
         </is>
       </c>
       <c r="BP36" s="20" t="inlineStr">
         <is>
-          <t>45.5 x 37.2 x 27.5 cm</t>
+          <t>48 x 36 x 20.5 cm</t>
         </is>
       </c>
       <c r="BQ36" s="20" t="inlineStr">
         <is>
-          <t>45.50 x 37.20 x 27.50 cm</t>
+          <t>48.00 x 36.00 x 20.50 cm</t>
         </is>
       </c>
       <c r="BR36" s="11" t="inlineStr">
@@ -15712,40 +15436,40 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B087Z4YF8S</t>
+          <t>B0DW45FNFD</t>
         </is>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B087Z4YF8S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JIGOO</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 被褥清洁剂 大功率模型 防螨 宽头 拍打 约14000次/分钟 IC-FAC</t>
+          <t>JIGOO S100 Gigo 被褥吸尘器 1.3千克 超轻被子用吸尘器s55℃ 热风干燥 UV 消毒 12KPa 强吸力约 80,000 次/分钟快速拍 230 毫米超宽吸嘴螨传感器 LED 显示屏兼容床垫、床、沙发、地毯、宠物毛发</t>
         </is>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B087Z4YF8S?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DW45FNFD?psc=1</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51FXGYp5BcL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71332p8jV1L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>B087Z4YF8S</t>
+          <t>B0DW45FNFD</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
@@ -15759,13 +15483,13 @@
         </is>
       </c>
       <c r="O37" s="13">
-        <v>164886</v>
+        <v>235522</v>
       </c>
       <c r="P37" s="13">
-        <v>-25857</v>
+        <v>-29949</v>
       </c>
       <c r="Q37" s="14">
-        <v>-0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="R37" s="15" t="inlineStr">
         <is>
@@ -15774,57 +15498,55 @@
       </c>
       <c r="S37" s="16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T37" s="13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U37" s="14">
-        <v>-0.07</v>
+        <v>0.67</v>
       </c>
       <c r="V37" s="13">
-        <v>97500</v>
+        <v>79900</v>
       </c>
       <c r="W37" s="13"/>
       <c r="X37" s="13"/>
       <c r="Y37" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" s="13">
-        <v>21500</v>
+        <v>7990</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
-      <c r="AC37" s="13">
-        <v>57</v>
-      </c>
+      <c r="AC37" s="13"/>
       <c r="AD37" s="17">
-        <v>1272</v>
+        <v>50</v>
       </c>
       <c r="AE37" s="13">
         <v>2</v>
       </c>
       <c r="AF37" s="18">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG37" s="19">
-        <v>0.1333</v>
+        <v>0.2</v>
       </c>
       <c r="AH37" s="13">
-        <v>781</v>
+        <v>472</v>
       </c>
       <c r="AI37" s="14">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="11" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AL37" s="17">
-        <v>2349</v>
+        <v>306</v>
       </c>
       <c r="AM37" s="11" t="inlineStr">
         <is>
@@ -15835,14 +15557,14 @@
       <c r="AO37" s="11"/>
       <c r="AP37"/>
       <c r="AQ37" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR37" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS37" s="12" t="inlineStr">
         <is>
-          <t>スケチヨ商店(適格請求書発行事業者)</t>
+          <t>Qifan shop</t>
         </is>
       </c>
       <c r="AT37" s="11" t="inlineStr">
@@ -15852,21 +15574,25 @@
       </c>
       <c r="AU37" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV37" s="12" t="inlineStr">
         <is>
-          <t>三原市 広島県 7230052 JP</t>
+          <t>Tuen Mun Hong Kong 999077 HK</t>
         </is>
       </c>
       <c r="AW37" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JLEXPXXTRB24</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UV5G74OMRQ0L</t>
         </is>
       </c>
       <c r="AX37" s="11"/>
-      <c r="AY37" s="11"/>
+      <c r="AY37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ37" s="11"/>
       <c r="BA37" s="11"/>
       <c r="BB37" s="11"/>
@@ -15884,50 +15610,50 @@
       <c r="BF37" s="11"/>
       <c r="BG37" s="11"/>
       <c r="BH37" s="12"/>
-      <c r="BI37" s="20"/>
+      <c r="BI37" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ37" s="20" t="inlineStr">
         <is>
-          <t>2.2 kg</t>
+          <t>1.7 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="20" t="inlineStr">
         <is>
-          <t>2.20 kg</t>
+          <t>1.70 kg</t>
         </is>
       </c>
       <c r="BL37" s="20" t="inlineStr">
         <is>
-          <t>50.1 x 30 x 21.8 cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="20" t="inlineStr">
-        <is>
-          <t>50.10 x 30.00 x 21.80 cm</t>
-        </is>
-      </c>
+          <t>28.7長さ x 23幅 x 18.6高さ cm</t>
+        </is>
+      </c>
+      <c r="BM37" s="20"/>
       <c r="BN37" s="20" t="inlineStr">
         <is>
-          <t>3 kg</t>
+          <t>1.7 kg</t>
         </is>
       </c>
       <c r="BO37" s="20" t="inlineStr">
         <is>
-          <t>3.00 kg</t>
+          <t>1.70 kg</t>
         </is>
       </c>
       <c r="BP37" s="20" t="inlineStr">
         <is>
-          <t>48 x 36 x 20.5 cm</t>
+          <t>31.5 x 25.7 x 19 cm</t>
         </is>
       </c>
       <c r="BQ37" s="20" t="inlineStr">
         <is>
-          <t>48.00 x 36.00 x 20.50 cm</t>
+          <t>31.50 x 25.70 x 19.00 cm</t>
         </is>
       </c>
       <c r="BR37" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -15938,40 +15664,40 @@
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>B0H6FF5LHZ</t>
+          <t>B0GTTTTP71</t>
         </is>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>pronala</t>
+          <t>ノーブランド品</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=pronala</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>尘箱【除霉真神】超强吸霉全天候清洁净化器【除尘】强力 多功能 24小时自动吸附灰尘 大容量 省时打扫健康呼吸空间 家庭 客厅 卧室 厨房 托儿所 宠物区适用 (6)</t>
+          <t>被褥清洁剂 榻榻米次数 每分钟7000次 搭载螨虫检测传感器 白色 FCA-A3-W</t>
         </is>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H6FF5LHZ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GTTTTP71?psc=1</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/711Q4UmnGjL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/41t94rJieZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>B0H6FF5LHZ</t>
+          <t>B0GTTTTP71</t>
         </is>
       </c>
       <c r="M38" s="12" t="inlineStr">
@@ -15985,13 +15711,13 @@
         </is>
       </c>
       <c r="O38" s="13">
-        <v>87652</v>
+        <v>102319</v>
       </c>
       <c r="P38" s="13">
-        <v>84932</v>
+        <v>1015</v>
       </c>
       <c r="Q38" s="14">
-        <v>0.49</v>
+        <v>0.01</v>
       </c>
       <c r="R38" s="15" t="inlineStr">
         <is>
@@ -16000,36 +15726,32 @@
       </c>
       <c r="S38" s="16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T38" s="13">
-        <v>23</v>
-      </c>
-      <c r="U38" s="14"/>
+        <v>9</v>
+      </c>
+      <c r="U38" s="14">
+        <v>0</v>
+      </c>
       <c r="V38" s="13">
-        <v>80224</v>
+        <v>71865</v>
       </c>
       <c r="W38" s="13"/>
       <c r="X38" s="13"/>
       <c r="Y38" s="17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z38" s="13">
-        <v>3488</v>
+        <v>7985</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="13"/>
-      <c r="AD38" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE38" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="18">
-        <v>5</v>
-      </c>
+      <c r="AD38" s="17"/>
+      <c r="AE38" s="13"/>
+      <c r="AF38" s="18"/>
       <c r="AG38" s="19">
         <v>0</v>
       </c>
@@ -16040,11 +15762,11 @@
       <c r="AJ38"/>
       <c r="AK38" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AL38" s="17">
-        <v>29</v>
+        <v>196</v>
       </c>
       <c r="AM38" s="11" t="inlineStr">
         <is>
@@ -16055,14 +15777,14 @@
       <c r="AO38" s="11"/>
       <c r="AP38"/>
       <c r="AQ38" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR38" s="17">
         <v>1</v>
       </c>
       <c r="AS38" s="12" t="inlineStr">
         <is>
-          <t>配送3～11日以内PronalaShop-JP</t>
+          <t>JianShengTool</t>
         </is>
       </c>
       <c r="AT38" s="11" t="inlineStr">
@@ -16077,12 +15799,12 @@
       </c>
       <c r="AV38" s="12" t="inlineStr">
         <is>
-          <t>高新技术产业开发区玉兰街与月桂路交叉口</t>
+          <t>太原市 山西 030000 CN</t>
         </is>
       </c>
       <c r="AW38" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TBQ5YA5MO311</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XC24KSDSD196</t>
         </is>
       </c>
       <c r="AX38" s="11"/>
@@ -16099,11 +15821,7 @@
       <c r="BI38" s="20"/>
       <c r="BJ38" s="20"/>
       <c r="BK38" s="20"/>
-      <c r="BL38" s="20" t="inlineStr">
-        <is>
-          <t>10長さ x 10幅 x 10高さ mm</t>
-        </is>
-      </c>
+      <c r="BL38" s="20"/>
       <c r="BM38" s="20"/>
       <c r="BN38" s="20"/>
       <c r="BO38" s="20"/>
@@ -16118,40 +15836,40 @@
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>B0DW45FNFD</t>
+          <t>B0DTXHF87N</t>
         </is>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JIGOO</t>
+          <t>https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DTXHF87N&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>JIGOO S100 Gigo 被褥吸尘器 1.3千克 超轻被子用吸尘器s55℃ 热风干燥 UV 消毒 12KPa 强吸力约 80,000 次/分钟快速拍 230 毫米超宽吸嘴螨传感器 LED 显示屏兼容床垫、床、沙发、地毯、宠物毛发</t>
+          <t>HAUSHOF 被褥清洁剂 被褥吸尘器 除螨 防螨 UV除菌 超声波除菌 负离子产生功能 16kPa强力吸力 60℃高温加热技术 灰尘检测传感器 HEPA过滤器 工作状态指示灯 床 沙发 地毯 清洁</t>
         </is>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DW45FNFD?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DTXHF87N?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71332p8jV1L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/616ONjp63mL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0DW45FNFD</t>
+          <t>B0DTXHF87N</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
@@ -16165,13 +15883,13 @@
         </is>
       </c>
       <c r="O39" s="13">
-        <v>235522</v>
+        <v>91847</v>
       </c>
       <c r="P39" s="13">
-        <v>-29949</v>
+        <v>231651</v>
       </c>
       <c r="Q39" s="14">
-        <v>-0.15</v>
+        <v>0.72</v>
       </c>
       <c r="R39" s="15" t="inlineStr">
         <is>
@@ -16180,17 +15898,17 @@
       </c>
       <c r="S39" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T39" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U39" s="14">
-        <v>0.67</v>
+        <v>1.83</v>
       </c>
       <c r="V39" s="13">
-        <v>79900</v>
+        <v>59880</v>
       </c>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
@@ -16198,83 +15916,79 @@
         <v>1</v>
       </c>
       <c r="Z39" s="13">
-        <v>7990</v>
+        <v>9980</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="13"/>
       <c r="AD39" s="17">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AE39" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF39" s="18">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AG39" s="19">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH39" s="13">
-        <v>472</v>
+        <v>675</v>
       </c>
       <c r="AI39" s="14">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="11" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="AL39" s="17">
-        <v>306</v>
+        <v>573</v>
       </c>
       <c r="AM39" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN39" s="11"/>
       <c r="AO39" s="11"/>
       <c r="AP39"/>
       <c r="AQ39" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR39" s="17">
         <v>1</v>
       </c>
       <c r="AS39" s="12" t="inlineStr">
         <is>
-          <t>Qifan shop</t>
+          <t>Megastar Store</t>
         </is>
       </c>
       <c r="AT39" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU39" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV39" s="12" t="inlineStr">
         <is>
-          <t>Tuen Mun Hong Kong 999077 HK</t>
+          <t>No.35 Jiuhuan Road, Jiubao Town,</t>
         </is>
       </c>
       <c r="AW39" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UV5G74OMRQ0L</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES</t>
         </is>
       </c>
       <c r="AX39" s="11"/>
-      <c r="AY39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY39" s="11"/>
       <c r="AZ39" s="11"/>
       <c r="BA39" s="11"/>
       <c r="BB39" s="11"/>
@@ -16292,50 +16006,46 @@
       <c r="BF39" s="11"/>
       <c r="BG39" s="11"/>
       <c r="BH39" s="12"/>
-      <c r="BI39" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI39" s="20"/>
       <c r="BJ39" s="20" t="inlineStr">
         <is>
-          <t>1.7 Kilograms</t>
+          <t>1.9 kg</t>
         </is>
       </c>
       <c r="BK39" s="20" t="inlineStr">
         <is>
-          <t>1.70 kg</t>
+          <t>1.90 kg</t>
         </is>
       </c>
       <c r="BL39" s="20" t="inlineStr">
         <is>
-          <t>28.7長さ x 23幅 x 18.6高さ cm</t>
+          <t>29長さ x 24幅 x 20.8高さ cm</t>
         </is>
       </c>
       <c r="BM39" s="20"/>
       <c r="BN39" s="20" t="inlineStr">
         <is>
-          <t>1.7 kg</t>
+          <t>2.52 kg</t>
         </is>
       </c>
       <c r="BO39" s="20" t="inlineStr">
         <is>
-          <t>1.70 kg</t>
+          <t>2.52 kg</t>
         </is>
       </c>
       <c r="BP39" s="20" t="inlineStr">
         <is>
-          <t>31.5 x 25.7 x 19 cm</t>
+          <t>32.7 x 28.7 x 25.4 cm</t>
         </is>
       </c>
       <c r="BQ39" s="20" t="inlineStr">
         <is>
-          <t>31.50 x 25.70 x 19.00 cm</t>
+          <t>32.70 x 28.70 x 25.40 cm</t>
         </is>
       </c>
       <c r="BR39" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -16346,40 +16056,40 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0GTTTTP71</t>
+          <t>B086D6FKJJ</t>
         </is>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>ノーブランド品</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B086D6FKJJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>被褥清洁剂 榻榻米次数 每分钟7000次 搭载螨虫检测传感器 白色 FCA-A3-W</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 AC被褥清洁剂 大功率 玫瑰金 KIC-FAC4</t>
         </is>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GTTTTP71?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B086D6FKJJ?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41t94rJieZL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51m1MS9FICL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0GTTTTP71</t>
+          <t>B086D6FKJJ</t>
         </is>
       </c>
       <c r="M40" s="12" t="inlineStr">
@@ -16393,13 +16103,13 @@
         </is>
       </c>
       <c r="O40" s="13">
-        <v>102319</v>
+        <v>363035</v>
       </c>
       <c r="P40" s="13">
-        <v>1015</v>
+        <v>-44121</v>
       </c>
       <c r="Q40" s="14">
-        <v>0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="R40" s="15" t="inlineStr">
         <is>
@@ -16408,17 +16118,15 @@
       </c>
       <c r="S40" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>75</t>
         </is>
       </c>
       <c r="T40" s="13">
-        <v>9</v>
-      </c>
-      <c r="U40" s="14">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U40" s="14"/>
       <c r="V40" s="13">
-        <v>71865</v>
+        <v>41820</v>
       </c>
       <c r="W40" s="13"/>
       <c r="X40" s="13"/>
@@ -16426,67 +16134,75 @@
         <v>1</v>
       </c>
       <c r="Z40" s="13">
-        <v>7985</v>
+        <v>29800</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="13"/>
-      <c r="AD40" s="17"/>
-      <c r="AE40" s="13"/>
-      <c r="AF40" s="18"/>
+      <c r="AD40" s="17">
+        <v>84</v>
+      </c>
+      <c r="AE40" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="18">
+        <v>4.1</v>
+      </c>
       <c r="AG40" s="19">
         <v>0</v>
       </c>
-      <c r="AH40" s="13"/>
+      <c r="AH40" s="13">
+        <v>781</v>
+      </c>
       <c r="AI40" s="14">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2020-05-02</t>
         </is>
       </c>
       <c r="AL40" s="17">
-        <v>196</v>
+        <v>2350</v>
       </c>
       <c r="AM40" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN40" s="11"/>
       <c r="AO40" s="11"/>
       <c r="AP40"/>
       <c r="AQ40" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AR40" s="17">
         <v>1</v>
       </c>
       <c r="AS40" s="12" t="inlineStr">
         <is>
-          <t>JianShengTool</t>
+          <t>makana1001</t>
         </is>
       </c>
       <c r="AT40" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU40" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV40" s="12" t="inlineStr">
         <is>
-          <t>太原市 山西 030000 CN</t>
+          <t>江東区 東京都 1350063 JP</t>
         </is>
       </c>
       <c r="AW40" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XC24KSDSD196</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQU7G7SXPENAQ</t>
         </is>
       </c>
       <c r="AX40" s="11"/>
@@ -16494,22 +16210,62 @@
       <c r="AZ40" s="11"/>
       <c r="BA40" s="11"/>
       <c r="BB40" s="11"/>
-      <c r="BC40" s="11"/>
+      <c r="BC40" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD40" s="11"/>
       <c r="BE40" s="11"/>
       <c r="BF40" s="11"/>
       <c r="BG40" s="11"/>
       <c r="BH40" s="12"/>
       <c r="BI40" s="20"/>
-      <c r="BJ40" s="20"/>
-      <c r="BK40" s="20"/>
-      <c r="BL40" s="20"/>
-      <c r="BM40" s="20"/>
-      <c r="BN40" s="20"/>
-      <c r="BO40" s="20"/>
-      <c r="BP40" s="20"/>
-      <c r="BQ40" s="20"/>
-      <c r="BR40" s="11"/>
+      <c r="BJ40" s="20" t="inlineStr">
+        <is>
+          <t>3.58 kg</t>
+        </is>
+      </c>
+      <c r="BK40" s="20" t="inlineStr">
+        <is>
+          <t>3.58 kg</t>
+        </is>
+      </c>
+      <c r="BL40" s="20" t="inlineStr">
+        <is>
+          <t>48.4 x 36.8 x 21.6 cm</t>
+        </is>
+      </c>
+      <c r="BM40" s="20" t="inlineStr">
+        <is>
+          <t>48.40 x 36.80 x 21.60 cm</t>
+        </is>
+      </c>
+      <c r="BN40" s="20" t="inlineStr">
+        <is>
+          <t>3.58 kg</t>
+        </is>
+      </c>
+      <c r="BO40" s="20" t="inlineStr">
+        <is>
+          <t>3.58 kg</t>
+        </is>
+      </c>
+      <c r="BP40" s="20" t="inlineStr">
+        <is>
+          <t>48.4 x 36.8 x 21.6 cm</t>
+        </is>
+      </c>
+      <c r="BQ40" s="20" t="inlineStr">
+        <is>
+          <t>48.40 x 36.80 x 21.60 cm</t>
+        </is>
+      </c>
+      <c r="BR40" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
@@ -16518,40 +16274,40 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B0DY61ZS3S</t>
+          <t>B00NII5XEE</t>
         </is>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン)</t>
+          <t>RAYCOP(レイコップ)</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0DY61ZS3S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B00NII5XEE&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>戴森 原装 戴森 Fton 工具2 500 [平行进口商品]</t>
+          <t>Raycop Japan 被褥清洁剂 RAYCOP RT 珍珠白 RT-300JWH</t>
         </is>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DY61ZS3S?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B00NII5XEE?psc=1</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/31dizVJn3lL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51x2VvwoIaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>B0DY61ZS3S</t>
+          <t>B00NII5XEE</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
@@ -16565,13 +16321,13 @@
         </is>
       </c>
       <c r="O41" s="13">
-        <v>208711</v>
+        <v>186586</v>
       </c>
       <c r="P41" s="13">
-        <v>-25272</v>
+        <v>89824</v>
       </c>
       <c r="Q41" s="14">
-        <v>-0.14</v>
+        <v>0.33</v>
       </c>
       <c r="R41" s="15" t="inlineStr">
         <is>
@@ -16580,15 +16336,15 @@
       </c>
       <c r="S41" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T41" s="13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U41" s="14"/>
       <c r="V41" s="13">
-        <v>69720</v>
+        <v>27860</v>
       </c>
       <c r="W41" s="13"/>
       <c r="X41" s="13"/>
@@ -16596,60 +16352,60 @@
         <v>1</v>
       </c>
       <c r="Z41" s="13">
-        <v>4930</v>
+        <v>3980</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="13"/>
       <c r="AD41" s="17">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE41" s="13">
         <v>0</v>
       </c>
       <c r="AF41" s="18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG41" s="19">
         <v>0</v>
       </c>
       <c r="AH41" s="13">
-        <v>425</v>
+        <v>532</v>
       </c>
       <c r="AI41" s="14">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="11" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2014-10-18</t>
         </is>
       </c>
       <c r="AL41" s="17">
-        <v>591</v>
+        <v>4372</v>
       </c>
       <c r="AM41" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN41" s="11"/>
       <c r="AO41" s="11"/>
       <c r="AP41"/>
       <c r="AQ41" s="17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AR41" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS41" s="12" t="inlineStr">
         <is>
-          <t>OMITSU</t>
+          <t>モリハウス</t>
         </is>
       </c>
       <c r="AT41" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU41" s="11" t="inlineStr">
@@ -16659,12 +16415,12 @@
       </c>
       <c r="AV41" s="12" t="inlineStr">
         <is>
-          <t>藤岡 群馬県 3750024 JP</t>
+          <t>守口市竹町 大阪府 5700086 JP</t>
         </is>
       </c>
       <c r="AW41" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ZTSKKP4W4CQ6</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS</t>
         </is>
       </c>
       <c r="AX41" s="11"/>
@@ -16681,38 +16437,42 @@
       <c r="BI41" s="20"/>
       <c r="BJ41" s="20" t="inlineStr">
         <is>
-          <t>60 g</t>
+          <t>2.43 Kilograms</t>
         </is>
       </c>
       <c r="BK41" s="20" t="inlineStr">
         <is>
-          <t>60.00 g</t>
+          <t>2.43 kg</t>
         </is>
       </c>
       <c r="BL41" s="20" t="inlineStr">
         <is>
-          <t>19長さ x 12幅 x 4.5高さ cm</t>
-        </is>
-      </c>
-      <c r="BM41" s="20"/>
+          <t>35.5 x 31.1 x 17.9 cm</t>
+        </is>
+      </c>
+      <c r="BM41" s="20" t="inlineStr">
+        <is>
+          <t>35.50 x 31.10 x 17.90 cm</t>
+        </is>
+      </c>
       <c r="BN41" s="20" t="inlineStr">
         <is>
-          <t>160 g</t>
+          <t>2.43 kg</t>
         </is>
       </c>
       <c r="BO41" s="20" t="inlineStr">
         <is>
-          <t>160.00 g</t>
+          <t>2.43 kg</t>
         </is>
       </c>
       <c r="BP41" s="20" t="inlineStr">
         <is>
-          <t>21.9 x 17.8 x 5.7 cm</t>
+          <t>35.5 x 31.1 x 17.9 cm</t>
         </is>
       </c>
       <c r="BQ41" s="20" t="inlineStr">
         <is>
-          <t>21.90 x 17.80 x 5.70 cm</t>
+          <t>35.50 x 31.10 x 17.90 cm</t>
         </is>
       </c>
       <c r="BR41" s="11" t="inlineStr">
@@ -16728,40 +16488,40 @@
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>B0DTXHF87N</t>
+          <t>B0DH8B8TM4</t>
         </is>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="12"/>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>Neping</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DTXHF87N&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.jp/Neping/b/ref=bl_dp_s_web_23533992051?ie=UTF8&amp;node=23533992051&amp;field-lbr_brands_browse-bin=Neping</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>HAUSHOF 被褥清洁剂 被褥吸尘器 除螨 防螨 UV除菌 超声波除菌 负离子产生功能 16kPa强力吸力 60℃高温加热技术 灰尘检测传感器 HEPA过滤器 工作状态指示灯 床 沙发 地毯 清洁</t>
+          <t>螨虫吸尘器 蒲团吸尘器 小型吸尘器 被褥吸尘器 附带2个刷头 USB 充电式 手持式 手持式 无线・便携・除螨器 轻巧极简外观 家庭协调</t>
         </is>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DTXHF87N?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DH8B8TM4?psc=1</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/616ONjp63mL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/31bjNOyZF4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>B0DTXHF87N</t>
+          <t>B0DH8B8TM4</t>
         </is>
       </c>
       <c r="M42" s="12" t="inlineStr">
@@ -16775,13 +16535,13 @@
         </is>
       </c>
       <c r="O42" s="13">
-        <v>91847</v>
+        <v>173037</v>
       </c>
       <c r="P42" s="13">
-        <v>231651</v>
+        <v>-69664</v>
       </c>
       <c r="Q42" s="14">
-        <v>0.72</v>
+        <v>-0.67</v>
       </c>
       <c r="R42" s="15" t="inlineStr">
         <is>
@@ -16790,78 +16550,72 @@
       </c>
       <c r="S42" s="16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T42" s="13">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="U42" s="14">
-        <v>1.83</v>
+        <v>-0.86</v>
       </c>
       <c r="V42" s="13">
-        <v>59880</v>
+        <v>23786</v>
       </c>
       <c r="W42" s="13"/>
       <c r="X42" s="13"/>
       <c r="Y42" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="13">
-        <v>9980</v>
+        <v>1699</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="13"/>
-      <c r="AD42" s="17">
-        <v>11</v>
-      </c>
-      <c r="AE42" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="18">
-        <v>3.6</v>
-      </c>
+      <c r="AD42" s="17"/>
+      <c r="AE42" s="13"/>
+      <c r="AF42" s="18"/>
       <c r="AG42" s="19">
         <v>0</v>
       </c>
       <c r="AH42" s="13">
-        <v>675</v>
+        <v>420</v>
       </c>
       <c r="AI42" s="14">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="11" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AL42" s="17">
-        <v>573</v>
+        <v>669</v>
       </c>
       <c r="AM42" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN42" s="11"/>
       <c r="AO42" s="11"/>
       <c r="AP42"/>
       <c r="AQ42" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AR42" s="17">
         <v>1</v>
       </c>
       <c r="AS42" s="12" t="inlineStr">
         <is>
-          <t>Megastar Store</t>
+          <t>配送3～11日以内Neping Shop-JP</t>
         </is>
       </c>
       <c r="AT42" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU42" s="11" t="inlineStr">
@@ -16871,12 +16625,12 @@
       </c>
       <c r="AV42" s="12" t="inlineStr">
         <is>
-          <t>No.35 Jiuhuan Road, Jiubao Town,</t>
+          <t>郑州市 河南省 450000 CN</t>
         </is>
       </c>
       <c r="AW42" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJHJPPEGEZ4DJ</t>
         </is>
       </c>
       <c r="AX42" s="11"/>
@@ -16884,16 +16638,8 @@
       <c r="AZ42" s="11"/>
       <c r="BA42" s="11"/>
       <c r="BB42" s="11"/>
-      <c r="BC42" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD42" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC42" s="11"/>
+      <c r="BD42" s="11"/>
       <c r="BE42" s="11"/>
       <c r="BF42" s="11"/>
       <c r="BG42" s="11"/>
@@ -16901,43 +16647,43 @@
       <c r="BI42" s="20"/>
       <c r="BJ42" s="20" t="inlineStr">
         <is>
-          <t>1.9 kg</t>
+          <t>0.2 g</t>
         </is>
       </c>
       <c r="BK42" s="20" t="inlineStr">
         <is>
-          <t>1.90 kg</t>
+          <t>0.20 g</t>
         </is>
       </c>
       <c r="BL42" s="20" t="inlineStr">
         <is>
-          <t>29長さ x 24幅 x 20.8高さ cm</t>
+          <t>20長さ x 20幅 x 20高さ cm</t>
         </is>
       </c>
       <c r="BM42" s="20"/>
       <c r="BN42" s="20" t="inlineStr">
         <is>
-          <t>2.52 kg</t>
+          <t>360 g</t>
         </is>
       </c>
       <c r="BO42" s="20" t="inlineStr">
         <is>
-          <t>2.52 kg</t>
+          <t>360.00 g</t>
         </is>
       </c>
       <c r="BP42" s="20" t="inlineStr">
         <is>
-          <t>32.7 x 28.7 x 25.4 cm</t>
+          <t>17 x 15 x 6 cm</t>
         </is>
       </c>
       <c r="BQ42" s="20" t="inlineStr">
         <is>
-          <t>32.70 x 28.70 x 25.40 cm</t>
+          <t>17.00 x 15.00 x 6.00 cm</t>
         </is>
       </c>
       <c r="BR42" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -16948,40 +16694,40 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B0HJBYGLLS</t>
+          <t>B0DR1YK9LS</t>
         </is>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Yizibuur</t>
+          <t>エコジー</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Yizibuur/page/16D746F6-5F31-4921-AAB0-B9944FFD45C3?lp_asin=B0HJBYGLLS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A8%E3%82%B3%E3%82%B8%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%95/page/92446153-5DF5-46D6-8BDE-A3C30B3D3E3A?lp_asin=B0DR1YK9LS&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>防尘箱【除灰尘】多功能除尘箱【房屋灰尘的救星】 汽车 办公室 客厅 卧室 厨房 厕所用sMulti Functional Air Magic Box 只需放置即可自动吸尘强力小型吸尘器,迷你,24 小时自动吸附灰尘,快速去除灰尘,健康呼吸,对宝宝</t>
+          <t>布団クリーナー 布団掃除機 コードレス 1.2kg超軽量 UV除菌 18Kpa パワフルたたき コンパクト ウイルス除去 ダニ退治 マットレス 掃除 カーペット ベッド 花粉 ダニ対策 梅雨対策 ダニ取り掃除機 エコジー</t>
         </is>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HJBYGLLS?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41D9mkEdSsL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B0HJBYGLLS</t>
+          <t>B0DR1YK9LS</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
@@ -16995,13 +16741,13 @@
         </is>
       </c>
       <c r="O43" s="13">
-        <v>47394</v>
+        <v>200067</v>
       </c>
       <c r="P43" s="13">
-        <v>92579</v>
+        <v>-12116</v>
       </c>
       <c r="Q43" s="14">
-        <v>0.66</v>
+        <v>-0.06</v>
       </c>
       <c r="R43" s="15" t="inlineStr">
         <is>
@@ -17010,74 +16756,74 @@
       </c>
       <c r="S43" s="16" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="T43" s="13">
-        <v>35</v>
-      </c>
-      <c r="U43" s="14"/>
-      <c r="V43" s="13">
-        <v>50540</v>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="T43" s="13"/>
+      <c r="U43" s="14">
+        <v>-0.2</v>
+      </c>
+      <c r="V43" s="13"/>
       <c r="W43" s="13"/>
       <c r="X43" s="13"/>
       <c r="Y43" s="17">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="13">
-        <v>1444</v>
+        <v>9089</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="13"/>
       <c r="AD43" s="17">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AE43" s="13">
         <v>0</v>
       </c>
       <c r="AF43" s="18">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="AG43" s="19">
         <v>0</v>
       </c>
-      <c r="AH43" s="13"/>
+      <c r="AH43" s="13">
+        <v>675</v>
+      </c>
       <c r="AI43" s="14">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AL43" s="17">
-        <v>26</v>
+        <v>606</v>
       </c>
       <c r="AM43" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN43" s="11"/>
       <c r="AO43" s="11"/>
       <c r="AP43"/>
       <c r="AQ43" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR43" s="17">
         <v>1</v>
       </c>
       <c r="AS43" s="12" t="inlineStr">
         <is>
-          <t>XiZou e-commerce(跟卖必下单投诉）</t>
+          <t>Solesenyue</t>
         </is>
       </c>
       <c r="AT43" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU43" s="11" t="inlineStr">
@@ -17087,12 +16833,12 @@
       </c>
       <c r="AV43" s="12" t="inlineStr">
         <is>
-          <t>郑州市 河南 450000 CN</t>
+          <t>深圳市 龙岗区 广东省 518000 CN</t>
         </is>
       </c>
       <c r="AW43" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2Q4HC9SZPWZ92</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A13LYSKWCMFUWB</t>
         </is>
       </c>
       <c r="AX43" s="11"/>
@@ -17105,7 +16851,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD43" s="11"/>
+      <c r="BD43" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE43" s="11"/>
       <c r="BF43" s="11"/>
       <c r="BG43" s="11"/>
@@ -17113,33 +16863,45 @@
       <c r="BI43" s="20"/>
       <c r="BJ43" s="20" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>1.29 kg</t>
         </is>
       </c>
       <c r="BK43" s="20" t="inlineStr">
         <is>
-          <t>10.00 g</t>
+          <t>1.29 kg</t>
         </is>
       </c>
       <c r="BL43" s="20" t="inlineStr">
         <is>
-          <t>10長さ x 10幅 x 10高さ mm</t>
+          <t>25長さ x 29.8幅 x 20高さ cm</t>
         </is>
       </c>
       <c r="BM43" s="20"/>
       <c r="BN43" s="20" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>2.07 kg</t>
         </is>
       </c>
       <c r="BO43" s="20" t="inlineStr">
         <is>
-          <t>10.00 g</t>
-        </is>
-      </c>
-      <c r="BP43" s="20"/>
-      <c r="BQ43" s="20"/>
-      <c r="BR43" s="11"/>
+          <t>2.07 kg</t>
+        </is>
+      </c>
+      <c r="BP43" s="20" t="inlineStr">
+        <is>
+          <t>34.7 x 29.4 x 22.9 cm</t>
+        </is>
+      </c>
+      <c r="BQ43" s="20" t="inlineStr">
+        <is>
+          <t>34.70 x 29.40 x 22.90 cm</t>
+        </is>
+      </c>
+      <c r="BR43" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
@@ -17148,7 +16910,7 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B086D6FKJJ</t>
+          <t>B0H6BMMJJ2</t>
         </is>
       </c>
       <c r="D44" s="12"/>
@@ -17160,28 +16922,28 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B086D6FKJJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0H6BMMJJ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 AC被褥清洁剂 大功率 玫瑰金 KIC-FAC4</t>
+          <t>IRIS OHYAMA 爱丽思欧雅玛 充电式纸袋被褥清洁器 白色 FBD-41-W</t>
         </is>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B086D6FKJJ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51m1MS9FICL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/217kOnSQp6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>B086D6FKJJ</t>
+          <t>B0H6BMMJJ2</t>
         </is>
       </c>
       <c r="M44" s="12" t="inlineStr">
@@ -17195,13 +16957,13 @@
         </is>
       </c>
       <c r="O44" s="13">
-        <v>363035</v>
+        <v>64204</v>
       </c>
       <c r="P44" s="13">
-        <v>-44121</v>
+        <v>-36073</v>
       </c>
       <c r="Q44" s="14">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="R44" s="15" t="inlineStr">
         <is>
@@ -17210,76 +16972,62 @@
       </c>
       <c r="S44" s="16" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="T44" s="13">
-        <v>6</v>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="T44" s="13"/>
       <c r="U44" s="14"/>
-      <c r="V44" s="13">
-        <v>41820</v>
-      </c>
+      <c r="V44" s="13"/>
       <c r="W44" s="13"/>
       <c r="X44" s="13"/>
       <c r="Y44" s="17">
         <v>1</v>
       </c>
       <c r="Z44" s="13">
-        <v>29800</v>
+        <v>17680</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="13"/>
-      <c r="AD44" s="17">
-        <v>84</v>
-      </c>
-      <c r="AE44" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="18">
-        <v>4.1</v>
-      </c>
+      <c r="AD44" s="17"/>
+      <c r="AE44" s="13"/>
+      <c r="AF44" s="18"/>
       <c r="AG44" s="19">
         <v>0</v>
       </c>
-      <c r="AH44" s="13">
-        <v>781</v>
-      </c>
+      <c r="AH44" s="13"/>
       <c r="AI44" s="14">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="11" t="inlineStr">
         <is>
-          <t>2020-05-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AL44" s="17">
-        <v>2350</v>
+        <v>105</v>
       </c>
       <c r="AM44" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN44" s="11"/>
       <c r="AO44" s="11"/>
       <c r="AP44"/>
-      <c r="AQ44" s="17">
-        <v>10</v>
-      </c>
+      <c r="AQ44" s="17"/>
       <c r="AR44" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS44" s="12" t="inlineStr">
         <is>
-          <t>makana1001</t>
+          <t>イートレンド [適格請求書発行事業者登録済]</t>
         </is>
       </c>
       <c r="AT44" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU44" s="11" t="inlineStr">
@@ -17289,12 +17037,12 @@
       </c>
       <c r="AV44" s="12" t="inlineStr">
         <is>
-          <t>江東区 東京都 1350063 JP</t>
+          <t>神田須田町１－３４－３</t>
         </is>
       </c>
       <c r="AW44" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQU7G7SXPENAQ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A73TY2PE3Z2RH</t>
         </is>
       </c>
       <c r="AX44" s="11"/>
@@ -17302,1382 +17050,22 @@
       <c r="AZ44" s="11"/>
       <c r="BA44" s="11"/>
       <c r="BB44" s="11"/>
-      <c r="BC44" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC44" s="11"/>
       <c r="BD44" s="11"/>
       <c r="BE44" s="11"/>
       <c r="BF44" s="11"/>
       <c r="BG44" s="11"/>
       <c r="BH44" s="12"/>
       <c r="BI44" s="20"/>
-      <c r="BJ44" s="20" t="inlineStr">
-        <is>
-          <t>3.58 kg</t>
-        </is>
-      </c>
-      <c r="BK44" s="20" t="inlineStr">
-        <is>
-          <t>3.58 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="20" t="inlineStr">
-        <is>
-          <t>48.4 x 36.8 x 21.6 cm</t>
-        </is>
-      </c>
-      <c r="BM44" s="20" t="inlineStr">
-        <is>
-          <t>48.40 x 36.80 x 21.60 cm</t>
-        </is>
-      </c>
-      <c r="BN44" s="20" t="inlineStr">
-        <is>
-          <t>3.58 kg</t>
-        </is>
-      </c>
-      <c r="BO44" s="20" t="inlineStr">
-        <is>
-          <t>3.58 kg</t>
-        </is>
-      </c>
-      <c r="BP44" s="20" t="inlineStr">
-        <is>
-          <t>48.4 x 36.8 x 21.6 cm</t>
-        </is>
-      </c>
-      <c r="BQ44" s="20" t="inlineStr">
-        <is>
-          <t>48.40 x 36.80 x 21.60 cm</t>
-        </is>
-      </c>
-      <c r="BR44" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>B00NII5XEE</t>
-        </is>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>RAYCOP(レイコップ)</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B00NII5XEE&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>Raycop Japan 被褥清洁剂 RAYCOP RT 珍珠白 RT-300JWH</t>
-        </is>
-      </c>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B00NII5XEE?psc=1</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51x2VvwoIaL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>B00NII5XEE</t>
-        </is>
-      </c>
-      <c r="M45" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:布団クリーナー</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O45" s="13">
-        <v>186586</v>
-      </c>
-      <c r="P45" s="13">
-        <v>89824</v>
-      </c>
-      <c r="Q45" s="14">
-        <v>0.33</v>
-      </c>
-      <c r="R45" s="15" t="inlineStr">
-        <is>
-          <t>布団クリーナー</t>
-        </is>
-      </c>
-      <c r="S45" s="16" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="T45" s="13">
-        <v>7</v>
-      </c>
-      <c r="U45" s="14"/>
-      <c r="V45" s="13">
-        <v>27860</v>
-      </c>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="13">
-        <v>3980</v>
-      </c>
-      <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45" s="13"/>
-      <c r="AD45" s="17">
-        <v>13</v>
-      </c>
-      <c r="AE45" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="18">
-        <v>4</v>
-      </c>
-      <c r="AG45" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="13">
-        <v>532</v>
-      </c>
-      <c r="AI45" s="14">
-        <v>0.72</v>
-      </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="11" t="inlineStr">
-        <is>
-          <t>2014-10-18</t>
-        </is>
-      </c>
-      <c r="AL45" s="17">
-        <v>4372</v>
-      </c>
-      <c r="AM45" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN45" s="11"/>
-      <c r="AO45" s="11"/>
-      <c r="AP45"/>
-      <c r="AQ45" s="17">
-        <v>7</v>
-      </c>
-      <c r="AR45" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS45" s="12" t="inlineStr">
-        <is>
-          <t>モリハウス</t>
-        </is>
-      </c>
-      <c r="AT45" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU45" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV45" s="12" t="inlineStr">
-        <is>
-          <t>守口市竹町 大阪府 5700086 JP</t>
-        </is>
-      </c>
-      <c r="AW45" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS</t>
-        </is>
-      </c>
-      <c r="AX45" s="11"/>
-      <c r="AY45" s="11"/>
-      <c r="AZ45" s="11"/>
-      <c r="BA45" s="11"/>
-      <c r="BB45" s="11"/>
-      <c r="BC45" s="11"/>
-      <c r="BD45" s="11"/>
-      <c r="BE45" s="11"/>
-      <c r="BF45" s="11"/>
-      <c r="BG45" s="11"/>
-      <c r="BH45" s="12"/>
-      <c r="BI45" s="20"/>
-      <c r="BJ45" s="20" t="inlineStr">
-        <is>
-          <t>2.43 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK45" s="20" t="inlineStr">
-        <is>
-          <t>2.43 kg</t>
-        </is>
-      </c>
-      <c r="BL45" s="20" t="inlineStr">
-        <is>
-          <t>35.5 x 31.1 x 17.9 cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="20" t="inlineStr">
-        <is>
-          <t>35.50 x 31.10 x 17.90 cm</t>
-        </is>
-      </c>
-      <c r="BN45" s="20" t="inlineStr">
-        <is>
-          <t>2.43 kg</t>
-        </is>
-      </c>
-      <c r="BO45" s="20" t="inlineStr">
-        <is>
-          <t>2.43 kg</t>
-        </is>
-      </c>
-      <c r="BP45" s="20" t="inlineStr">
-        <is>
-          <t>35.5 x 31.1 x 17.9 cm</t>
-        </is>
-      </c>
-      <c r="BQ45" s="20" t="inlineStr">
-        <is>
-          <t>35.50 x 31.10 x 17.90 cm</t>
-        </is>
-      </c>
-      <c r="BR45" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>45</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>B0DH8B8TM4</t>
-        </is>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Neping</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/Neping/b/ref=bl_dp_s_web_23533992051?ie=UTF8&amp;node=23533992051&amp;field-lbr_brands_browse-bin=Neping</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>螨虫吸尘器 蒲团吸尘器 小型吸尘器 被褥吸尘器 附带2个刷头 USB 充电式 手持式 手持式 无线・便携・除螨器 轻巧极简外观 家庭协调</t>
-        </is>
-      </c>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0DH8B8TM4?psc=1</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/31bjNOyZF4L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>B0DH8B8TM4</t>
-        </is>
-      </c>
-      <c r="M46" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:布団クリーナー</t>
-        </is>
-      </c>
-      <c r="N46" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O46" s="13">
-        <v>173037</v>
-      </c>
-      <c r="P46" s="13">
-        <v>-69664</v>
-      </c>
-      <c r="Q46" s="14">
-        <v>-0.67</v>
-      </c>
-      <c r="R46" s="15" t="inlineStr">
-        <is>
-          <t>布団クリーナー</t>
-        </is>
-      </c>
-      <c r="S46" s="16" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="T46" s="13">
-        <v>14</v>
-      </c>
-      <c r="U46" s="14">
-        <v>-0.86</v>
-      </c>
-      <c r="V46" s="13">
-        <v>23786</v>
-      </c>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="17">
-        <v>2</v>
-      </c>
-      <c r="Z46" s="13">
-        <v>1699</v>
-      </c>
-      <c r="AA46"/>
-      <c r="AB46"/>
-      <c r="AC46" s="13"/>
-      <c r="AD46" s="17"/>
-      <c r="AE46" s="13"/>
-      <c r="AF46" s="18"/>
-      <c r="AG46" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="13">
-        <v>420</v>
-      </c>
-      <c r="AI46" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="11" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AL46" s="17">
-        <v>669</v>
-      </c>
-      <c r="AM46" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AN46" s="11"/>
-      <c r="AO46" s="11"/>
-      <c r="AP46"/>
-      <c r="AQ46" s="17">
-        <v>6</v>
-      </c>
-      <c r="AR46" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS46" s="12" t="inlineStr">
-        <is>
-          <t>配送3～11日以内Neping Shop-JP</t>
-        </is>
-      </c>
-      <c r="AT46" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU46" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV46" s="12" t="inlineStr">
-        <is>
-          <t>郑州市 河南省 450000 CN</t>
-        </is>
-      </c>
-      <c r="AW46" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJHJPPEGEZ4DJ</t>
-        </is>
-      </c>
-      <c r="AX46" s="11"/>
-      <c r="AY46" s="11"/>
-      <c r="AZ46" s="11"/>
-      <c r="BA46" s="11"/>
-      <c r="BB46" s="11"/>
-      <c r="BC46" s="11"/>
-      <c r="BD46" s="11"/>
-      <c r="BE46" s="11"/>
-      <c r="BF46" s="11"/>
-      <c r="BG46" s="11"/>
-      <c r="BH46" s="12"/>
-      <c r="BI46" s="20"/>
-      <c r="BJ46" s="20" t="inlineStr">
-        <is>
-          <t>0.2 g</t>
-        </is>
-      </c>
-      <c r="BK46" s="20" t="inlineStr">
-        <is>
-          <t>0.20 g</t>
-        </is>
-      </c>
-      <c r="BL46" s="20" t="inlineStr">
-        <is>
-          <t>20長さ x 20幅 x 20高さ cm</t>
-        </is>
-      </c>
-      <c r="BM46" s="20"/>
-      <c r="BN46" s="20" t="inlineStr">
-        <is>
-          <t>360 g</t>
-        </is>
-      </c>
-      <c r="BO46" s="20" t="inlineStr">
-        <is>
-          <t>360.00 g</t>
-        </is>
-      </c>
-      <c r="BP46" s="20" t="inlineStr">
-        <is>
-          <t>17 x 15 x 6 cm</t>
-        </is>
-      </c>
-      <c r="BQ46" s="20" t="inlineStr">
-        <is>
-          <t>17.00 x 15.00 x 6.00 cm</t>
-        </is>
-      </c>
-      <c r="BR46" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>B0GGHC2648</t>
-        </is>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>Cociliye</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/stores/Cociliye/page/A132712C-622E-4322-A6B1-CC60DBFB2A1C?lp_asin=B0GGHCSSRC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>2026アップグレード版【ホコリ退治】ダストクリーンボックス 多機能吸着ボックス 置くだけ自動吸塵ボックス 強力 小型掃除機 24時間自動でホコリを吸着 ホコリを素早く除去 健やかな呼吸 赤ちゃんも安心使用 時短 &amp; 省力 Multi Functio</t>
-        </is>
-      </c>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GGHC2648?psc=1</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/7116SveneNL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>B0GGHC2648</t>
-        </is>
-      </c>
-      <c r="M47" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:布団クリーナー</t>
-        </is>
-      </c>
-      <c r="N47" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O47" s="13">
-        <v>129027</v>
-      </c>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="14">
-        <v>0</v>
-      </c>
-      <c r="R47" s="15" t="inlineStr">
-        <is>
-          <t>布団クリーナー</t>
-        </is>
-      </c>
-      <c r="S47" s="16" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="T47" s="13">
-        <v>1</v>
-      </c>
-      <c r="U47" s="14"/>
-      <c r="V47" s="13">
-        <v>2388</v>
-      </c>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="17">
-        <v>6</v>
-      </c>
-      <c r="Z47" s="13">
-        <v>2388</v>
-      </c>
-      <c r="AA47"/>
-      <c r="AB47"/>
-      <c r="AC47" s="13"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="13"/>
-      <c r="AF47" s="18"/>
-      <c r="AG47" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="13"/>
-      <c r="AI47" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="11"/>
-      <c r="AL47" s="17"/>
-      <c r="AM47" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AN47" s="11"/>
-      <c r="AO47" s="11"/>
-      <c r="AP47"/>
-      <c r="AQ47" s="17">
-        <v>7</v>
-      </c>
-      <c r="AR47" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS47" s="12" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐Cociliye Kinnei shop（通常、7〜10日配達されます）</t>
-        </is>
-      </c>
-      <c r="AT47" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU47" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV47" s="12" t="inlineStr">
-        <is>
-          <t>郑州市 河南 450000 CN</t>
-        </is>
-      </c>
-      <c r="AW47" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UMUHBLLQ740B</t>
-        </is>
-      </c>
-      <c r="AX47" s="11"/>
-      <c r="AY47" s="11"/>
-      <c r="AZ47" s="11"/>
-      <c r="BA47" s="11"/>
-      <c r="BB47" s="11"/>
-      <c r="BC47" s="11"/>
-      <c r="BD47" s="11"/>
-      <c r="BE47" s="11"/>
-      <c r="BF47" s="11"/>
-      <c r="BG47" s="11"/>
-      <c r="BH47" s="12"/>
-      <c r="BI47" s="20"/>
-      <c r="BJ47" s="20"/>
-      <c r="BK47" s="20"/>
-      <c r="BL47" s="20"/>
-      <c r="BM47" s="20"/>
-      <c r="BN47" s="20"/>
-      <c r="BO47" s="20"/>
-      <c r="BP47" s="20"/>
-      <c r="BQ47" s="20"/>
-      <c r="BR47" s="11"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>B0GFMNZH8L</t>
-        </is>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JUELREOU</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU【除尘消除】集尘清洁箱【2026最新】 强力 24小时自动吸附灰尘 快速去除灰尘 健康呼吸 宝宝也可放心使用 Multi Functional Air Magic Box 汽车 办公室 客厅 卧室 厨房 厕所用 (新版4个)</t>
-        </is>
-      </c>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GFMNZH8L?psc=1</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41pnZeYlEhL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>B0GFMNZH8L</t>
-        </is>
-      </c>
-      <c r="M48" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:布団クリーナー</t>
-        </is>
-      </c>
-      <c r="N48" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O48" s="13">
-        <v>60553</v>
-      </c>
-      <c r="P48" s="13">
-        <v>309925</v>
-      </c>
-      <c r="Q48" s="14">
-        <v>0.73</v>
-      </c>
-      <c r="R48" s="15" t="inlineStr">
-        <is>
-          <t>布団クリーナー</t>
-        </is>
-      </c>
-      <c r="S48" s="16" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="T48" s="13">
-        <v>1</v>
-      </c>
-      <c r="U48" s="14">
-        <v>-1</v>
-      </c>
-      <c r="V48" s="13">
-        <v>1144</v>
-      </c>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="17">
-        <v>15</v>
-      </c>
-      <c r="Z48" s="13">
-        <v>1144</v>
-      </c>
-      <c r="AA48"/>
-      <c r="AB48"/>
-      <c r="AC48" s="13"/>
-      <c r="AD48" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE48" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="18">
-        <v>1</v>
-      </c>
-      <c r="AG48" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="13"/>
-      <c r="AI48" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="11"/>
-      <c r="AL48" s="17"/>
-      <c r="AM48" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AN48" s="11"/>
-      <c r="AO48" s="11"/>
-      <c r="AP48"/>
-      <c r="AQ48" s="17">
-        <v>7</v>
-      </c>
-      <c r="AR48" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS48" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU（通常、5〜10日配達されます）</t>
-        </is>
-      </c>
-      <c r="AT48" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU48" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV48" s="12" t="inlineStr">
-        <is>
-          <t>郑州市 河南 450000 CN</t>
-        </is>
-      </c>
-      <c r="AW48" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1VJKLQTDJXYI3</t>
-        </is>
-      </c>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="11"/>
-      <c r="BB48" s="11"/>
-      <c r="BC48" s="11"/>
-      <c r="BD48" s="11"/>
-      <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="11"/>
-      <c r="BH48" s="12"/>
-      <c r="BI48" s="20"/>
-      <c r="BJ48" s="20"/>
-      <c r="BK48" s="20"/>
-      <c r="BL48" s="20"/>
-      <c r="BM48" s="20"/>
-      <c r="BN48" s="20"/>
-      <c r="BO48" s="20"/>
-      <c r="BP48" s="20"/>
-      <c r="BQ48" s="20"/>
-      <c r="BR48" s="11"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>48</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>B0GCFFRYMW</t>
-        </is>
-      </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Vailaipupy</t>
-        </is>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/stores/%E9%AB%98%E5%93%81%E8%B3%AA%E3%81%A7%E6%89%8B%E9%A0%83%E3%81%AA%E4%BE%A1%E6%A0%BC%E3%81%AE%E5%95%86%E5%93%81%E3%82%92%E3%81%8A%E5%B1%8A%E3%81%91%E3%81%97%E3%81%BE%E3%81%99%E3%80%82/page/CBB43826-CEEB-4FCD-9B7C-350E46DDAFE0?lp_asin=B0GCFFRYMW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>[Vailaipupy]【除尘清洁箱【2026最新 房屋灰尘的救世主】多功能吸附盒 强力 小型吸尘器 只需放置即可自动吸尘箱 24小时自动吸附灰尘 快速去除灰尘 健康呼吸 宝宝也可放心使用 时间短 &amp; 省力 Multi Functional Air</t>
-        </is>
-      </c>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GCFFRYMW?psc=1</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61ajaiqPPWL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>B0GCFFRYMW</t>
-        </is>
-      </c>
-      <c r="M49" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:布団クリーナー</t>
-        </is>
-      </c>
-      <c r="N49" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O49" s="13">
-        <v>157011</v>
-      </c>
-      <c r="P49" s="13">
-        <v>619242</v>
-      </c>
-      <c r="Q49" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="R49" s="15" t="inlineStr">
-        <is>
-          <t>布団クリーナー</t>
-        </is>
-      </c>
-      <c r="S49" s="16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T49" s="13">
-        <v>1</v>
-      </c>
-      <c r="U49" s="14"/>
-      <c r="V49" s="13">
-        <v>498</v>
-      </c>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="13">
-        <v>1187</v>
-      </c>
-      <c r="AA49"/>
-      <c r="AB49"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="17"/>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="18"/>
-      <c r="AG49" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="13"/>
-      <c r="AI49" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="AL49" s="17">
-        <v>276</v>
-      </c>
-      <c r="AM49" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AN49" s="11"/>
-      <c r="AO49" s="11"/>
-      <c r="AP49"/>
-      <c r="AQ49" s="17">
-        <v>6</v>
-      </c>
-      <c r="AR49" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="12" t="inlineStr">
-        <is>
-          <t>Shugeng e-commerce（通常7〜10日配達されます）⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="AT49" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU49" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV49" s="12" t="inlineStr">
-        <is>
-          <t>郑州市 河南 450000 CN</t>
-        </is>
-      </c>
-      <c r="AW49" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23ENIU0LZSTG6</t>
-        </is>
-      </c>
-      <c r="AX49" s="11"/>
-      <c r="AY49" s="11"/>
-      <c r="AZ49" s="11"/>
-      <c r="BA49" s="11"/>
-      <c r="BB49" s="11"/>
-      <c r="BC49" s="11"/>
-      <c r="BD49" s="11"/>
-      <c r="BE49" s="11"/>
-      <c r="BF49" s="11"/>
-      <c r="BG49" s="11"/>
-      <c r="BH49" s="12"/>
-      <c r="BI49" s="20"/>
-      <c r="BJ49" s="20" t="inlineStr">
-        <is>
-          <t>50 g</t>
-        </is>
-      </c>
-      <c r="BK49" s="20" t="inlineStr">
-        <is>
-          <t>50.00 g</t>
-        </is>
-      </c>
-      <c r="BL49" s="20"/>
-      <c r="BM49" s="20"/>
-      <c r="BN49" s="20" t="inlineStr">
-        <is>
-          <t>100 g</t>
-        </is>
-      </c>
-      <c r="BO49" s="20" t="inlineStr">
-        <is>
-          <t>100.00 g</t>
-        </is>
-      </c>
-      <c r="BP49" s="20"/>
-      <c r="BQ49" s="20"/>
-      <c r="BR49" s="11"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>B0DR1YK9LS</t>
-        </is>
-      </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>エコジー</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A8%E3%82%B3%E3%82%B8%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%95/page/92446153-5DF5-46D6-8BDE-A3C30B3D3E3A?lp_asin=B0DR1YK9LS&amp;ref_=ast_bln</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>布団クリーナー 布団掃除機 コードレス 1.2kg超軽量 UV除菌 18Kpa パワフルたたき コンパクト ウイルス除去 ダニ退治 マットレス 掃除 カーペット ベッド 花粉 ダニ対策 梅雨対策 ダニ取り掃除機 エコジー</t>
-        </is>
-      </c>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>B0DR1YK9LS</t>
-        </is>
-      </c>
-      <c r="M50" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:布団クリーナー</t>
-        </is>
-      </c>
-      <c r="N50" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O50" s="13">
-        <v>200067</v>
-      </c>
-      <c r="P50" s="13">
-        <v>-12116</v>
-      </c>
-      <c r="Q50" s="14">
-        <v>-0.06</v>
-      </c>
-      <c r="R50" s="15" t="inlineStr">
-        <is>
-          <t>布団クリーナー</t>
-        </is>
-      </c>
-      <c r="S50" s="16" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="T50" s="13"/>
-      <c r="U50" s="14">
-        <v>-0.2</v>
-      </c>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="13">
-        <v>9089</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="13"/>
-      <c r="AD50" s="17">
-        <v>100</v>
-      </c>
-      <c r="AE50" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="18">
-        <v>3.7</v>
-      </c>
-      <c r="AG50" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="13">
-        <v>675</v>
-      </c>
-      <c r="AI50" s="14">
-        <v>0.78</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="11" t="inlineStr">
-        <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AL50" s="17">
-        <v>606</v>
-      </c>
-      <c r="AM50" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN50" s="11"/>
-      <c r="AO50" s="11"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="17">
-        <v>8</v>
-      </c>
-      <c r="AR50" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="12" t="inlineStr">
-        <is>
-          <t>Solesenyue</t>
-        </is>
-      </c>
-      <c r="AT50" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU50" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV50" s="12" t="inlineStr">
-        <is>
-          <t>深圳市 龙岗区 广东省 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW50" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A13LYSKWCMFUWB</t>
-        </is>
-      </c>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50" s="20"/>
-      <c r="BJ50" s="20" t="inlineStr">
-        <is>
-          <t>1.29 kg</t>
-        </is>
-      </c>
-      <c r="BK50" s="20" t="inlineStr">
-        <is>
-          <t>1.29 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="20" t="inlineStr">
-        <is>
-          <t>25長さ x 29.8幅 x 20高さ cm</t>
-        </is>
-      </c>
-      <c r="BM50" s="20"/>
-      <c r="BN50" s="20" t="inlineStr">
-        <is>
-          <t>2.07 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="20" t="inlineStr">
-        <is>
-          <t>2.07 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="20" t="inlineStr">
-        <is>
-          <t>34.7 x 29.4 x 22.9 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="20" t="inlineStr">
-        <is>
-          <t>34.70 x 29.40 x 22.90 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0H6BMMJJ2</t>
-        </is>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0H6BMMJJ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>IRIS OHYAMA 爱丽思欧雅玛 充电式纸袋被褥清洁器 白色 FBD-41-W</t>
-        </is>
-      </c>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/217kOnSQp6L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0H6BMMJJ2</t>
-        </is>
-      </c>
-      <c r="M51" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:布団クリーナー</t>
-        </is>
-      </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O51" s="13">
-        <v>64204</v>
-      </c>
-      <c r="P51" s="13">
-        <v>-36073</v>
-      </c>
-      <c r="Q51" s="14">
-        <v>-0.03</v>
-      </c>
-      <c r="R51" s="15" t="inlineStr">
-        <is>
-          <t>布団クリーナー</t>
-        </is>
-      </c>
-      <c r="S51" s="16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="13">
-        <v>17680</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="13"/>
-      <c r="AD51" s="17"/>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="18"/>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="13"/>
-      <c r="AI51" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AL51" s="17">
-        <v>105</v>
-      </c>
-      <c r="AM51" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51" s="17">
-        <v>3</v>
-      </c>
-      <c r="AS51" s="12" t="inlineStr">
-        <is>
-          <t>イートレンド [適格請求書発行事業者登録済]</t>
-        </is>
-      </c>
-      <c r="AT51" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU51" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV51" s="12" t="inlineStr">
-        <is>
-          <t>神田須田町１－３４－３</t>
-        </is>
-      </c>
-      <c r="AW51" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A73TY2PE3Z2RH</t>
-        </is>
-      </c>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51" s="20"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51" s="11"/>
+      <c r="BJ44" s="20"/>
+      <c r="BK44" s="20"/>
+      <c r="BL44" s="20"/>
+      <c r="BM44" s="20"/>
+      <c r="BN44" s="20"/>
+      <c r="BO44" s="20"/>
+      <c r="BP44" s="20"/>
+      <c r="BQ44" s="20"/>
+      <c r="BR44" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18842,253 +17230,197 @@
     <hyperlink ref="M21" r:id="rId157" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N21" r:id="rId158"/>
     <hyperlink ref="AW21" r:id="rId159" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NM0RY4ZM5YCM"/>
-    <hyperlink ref="C22" r:id="rId160" tooltip="https://www.amazon.co.jp/dp/B016UAX3VQ"/>
-    <hyperlink ref="G22" r:id="rId161" tooltip="https://www.amazon.co.jp/stores/%E3%83%91%E3%83%8A%E3%82%BD%E3%83%8B%E3%83%83%E3%82%AF/page/9050EF98-FCF6-43FC-8443-62F3CF3A646C?lp_asin=B016UAX3VQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J22" r:id="rId162" tooltip="https://www.amazon.co.jp/dp/B016UAX3VQ?psc=1"/>
-    <hyperlink ref="K22" r:id="rId163" tooltip="https://m.media-amazon.com/images/I/41UdWx+bhwL._AC_US600_.jpg"/>
-    <hyperlink ref="L22" r:id="rId164" tooltip="https://www.amazon.co.jp/dp/B016UAX3VQ"/>
+    <hyperlink ref="C22" r:id="rId160" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS"/>
+    <hyperlink ref="G22" r:id="rId161" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=EFSHREE"/>
+    <hyperlink ref="J22" r:id="rId162" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS?psc=1"/>
+    <hyperlink ref="K22" r:id="rId163" tooltip="https://m.media-amazon.com/images/I/31+u94XQLbL._AC_US600_.jpg"/>
+    <hyperlink ref="L22" r:id="rId164" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS"/>
     <hyperlink ref="M22" r:id="rId165" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N22" r:id="rId166"/>
-    <hyperlink ref="AW22" r:id="rId167" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24MAWLD4IUCCX"/>
-    <hyperlink ref="C23" r:id="rId168" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS"/>
-    <hyperlink ref="G23" r:id="rId169" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=EFSHREE"/>
-    <hyperlink ref="J23" r:id="rId170" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS?psc=1"/>
-    <hyperlink ref="K23" r:id="rId171" tooltip="https://m.media-amazon.com/images/I/31+u94XQLbL._AC_US600_.jpg"/>
-    <hyperlink ref="L23" r:id="rId172" tooltip="https://www.amazon.co.jp/dp/B0D7HWNDXS"/>
+    <hyperlink ref="AW22" r:id="rId167" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2DFDWLWCIL47K"/>
+    <hyperlink ref="C23" r:id="rId168" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C"/>
+    <hyperlink ref="G23" r:id="rId169" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B07RT2QD4C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J23" r:id="rId170" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C?psc=1"/>
+    <hyperlink ref="K23" r:id="rId171" tooltip="https://images-na.ssl-images-amazon.com/images/I/51aZRLkyoaL._AC_US600_.jpg"/>
+    <hyperlink ref="L23" r:id="rId172" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C"/>
     <hyperlink ref="M23" r:id="rId173" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N23" r:id="rId174"/>
-    <hyperlink ref="AW23" r:id="rId175" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2DFDWLWCIL47K"/>
-    <hyperlink ref="C24" r:id="rId176" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C"/>
-    <hyperlink ref="G24" r:id="rId177" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B07RT2QD4C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J24" r:id="rId178" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C?psc=1"/>
-    <hyperlink ref="K24" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/51aZRLkyoaL._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId180" tooltip="https://www.amazon.co.jp/dp/B07RT2QD4C"/>
+    <hyperlink ref="AW23" r:id="rId175" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A28J8GQ3UQRK50"/>
+    <hyperlink ref="C24" r:id="rId176" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V"/>
+    <hyperlink ref="G24" r:id="rId177" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JIGOO"/>
+    <hyperlink ref="J24" r:id="rId178" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V?psc=1"/>
+    <hyperlink ref="K24" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/81kvopazcOL._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId180" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V"/>
     <hyperlink ref="M24" r:id="rId181" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N24" r:id="rId182"/>
-    <hyperlink ref="AW24" r:id="rId183" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A28J8GQ3UQRK50"/>
-    <hyperlink ref="C25" r:id="rId184" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V"/>
-    <hyperlink ref="G25" r:id="rId185" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JIGOO"/>
-    <hyperlink ref="J25" r:id="rId186" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V?psc=1"/>
-    <hyperlink ref="K25" r:id="rId187" tooltip="https://images-na.ssl-images-amazon.com/images/I/81kvopazcOL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId188" tooltip="https://www.amazon.co.jp/dp/B0D1XQPH2V"/>
+    <hyperlink ref="AW24" r:id="rId183" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UV5G74OMRQ0L"/>
+    <hyperlink ref="C25" r:id="rId184" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA"/>
+    <hyperlink ref="G25" r:id="rId185" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B01GUPMJMA&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J25" r:id="rId186" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA?psc=1"/>
+    <hyperlink ref="K25" r:id="rId187" tooltip="https://m.media-amazon.com/images/I/31aFWaIaVDL._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId188" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA"/>
     <hyperlink ref="M25" r:id="rId189" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N25" r:id="rId190"/>
-    <hyperlink ref="AW25" r:id="rId191" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UV5G74OMRQ0L"/>
-    <hyperlink ref="C26" r:id="rId192" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA"/>
-    <hyperlink ref="G26" r:id="rId193" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B01GUPMJMA&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J26" r:id="rId194" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA?psc=1"/>
-    <hyperlink ref="K26" r:id="rId195" tooltip="https://m.media-amazon.com/images/I/31aFWaIaVDL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId196" tooltip="https://www.amazon.co.jp/dp/B01GUPMJMA"/>
+    <hyperlink ref="AW25" r:id="rId191" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR8B5CKEPZWTA"/>
+    <hyperlink ref="C26" r:id="rId192" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF"/>
+    <hyperlink ref="G26" r:id="rId193" tooltip="https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0F4WKGDNF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J26" r:id="rId194" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF?psc=1"/>
+    <hyperlink ref="K26" r:id="rId195" tooltip="https://images-na.ssl-images-amazon.com/images/I/61eXaPVVpIL._AC_US600_.jpg"/>
+    <hyperlink ref="L26" r:id="rId196" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF"/>
     <hyperlink ref="M26" r:id="rId197" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N26" r:id="rId198"/>
-    <hyperlink ref="AW26" r:id="rId199" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR8B5CKEPZWTA"/>
-    <hyperlink ref="C27" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF"/>
-    <hyperlink ref="G27" r:id="rId201" tooltip="https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0F4WKGDNF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J27" r:id="rId202" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF?psc=1"/>
-    <hyperlink ref="K27" r:id="rId203" tooltip="https://images-na.ssl-images-amazon.com/images/I/61eXaPVVpIL._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId204" tooltip="https://www.amazon.co.jp/dp/B0F4WKGDNF"/>
+    <hyperlink ref="AW26" r:id="rId199" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES"/>
+    <hyperlink ref="C27" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW"/>
+    <hyperlink ref="G27" r:id="rId201" tooltip="https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B09JFPJWRW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J27" r:id="rId202" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW?psc=1"/>
+    <hyperlink ref="K27" r:id="rId203" tooltip="https://images-na.ssl-images-amazon.com/images/I/61AL6xxWioL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId204" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW"/>
     <hyperlink ref="M27" r:id="rId205" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N27" r:id="rId206"/>
-    <hyperlink ref="AW27" r:id="rId207" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES"/>
-    <hyperlink ref="C28" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW"/>
-    <hyperlink ref="G28" r:id="rId209" tooltip="https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B09JFPJWRW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J28" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW?psc=1"/>
-    <hyperlink ref="K28" r:id="rId211" tooltip="https://images-na.ssl-images-amazon.com/images/I/61AL6xxWioL._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId212" tooltip="https://www.amazon.co.jp/dp/B09JFPJWRW"/>
+    <hyperlink ref="AW27" r:id="rId207" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A7VAMUSDN30F"/>
+    <hyperlink ref="C28" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ"/>
+    <hyperlink ref="G28" r:id="rId209" tooltip="https://www.amazon.co.jp/stores/JIMMY/page/A7D1BFC6-FA2F-4840-A78D-62132A51D89B?lp_asin=B0CRYZV8CQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J28" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ?psc=1"/>
+    <hyperlink ref="K28" r:id="rId211" tooltip="https://images-na.ssl-images-amazon.com/images/I/61nCrGLFc4L._AC_US600_.jpg"/>
+    <hyperlink ref="L28" r:id="rId212" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ"/>
     <hyperlink ref="M28" r:id="rId213" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N28" r:id="rId214"/>
-    <hyperlink ref="AW28" r:id="rId215" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A7VAMUSDN30F"/>
-    <hyperlink ref="C29" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ"/>
-    <hyperlink ref="G29" r:id="rId217" tooltip="https://www.amazon.co.jp/stores/JIMMY/page/A7D1BFC6-FA2F-4840-A78D-62132A51D89B?lp_asin=B0CRYZV8CQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J29" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ?psc=1"/>
-    <hyperlink ref="K29" r:id="rId219" tooltip="https://images-na.ssl-images-amazon.com/images/I/61nCrGLFc4L._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B0CRYZV8CQ"/>
+    <hyperlink ref="AW28" r:id="rId215" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A27XS3ZIJF6R09"/>
+    <hyperlink ref="C29" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B082C6KRNV"/>
+    <hyperlink ref="G29" r:id="rId217" tooltip="https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B082C6KRNV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J29" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B082C6KRNV?psc=1"/>
+    <hyperlink ref="K29" r:id="rId219" tooltip="https://images-na.ssl-images-amazon.com/images/I/71UnzlAVhEL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B082C6KRNV"/>
     <hyperlink ref="M29" r:id="rId221" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N29" r:id="rId222"/>
-    <hyperlink ref="AW29" r:id="rId223" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A27XS3ZIJF6R09"/>
-    <hyperlink ref="C30" r:id="rId224" tooltip="https://www.amazon.co.jp/dp/B082C6KRNV"/>
-    <hyperlink ref="G30" r:id="rId225" tooltip="https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B082C6KRNV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J30" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B082C6KRNV?psc=1"/>
-    <hyperlink ref="K30" r:id="rId227" tooltip="https://images-na.ssl-images-amazon.com/images/I/71UnzlAVhEL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B082C6KRNV"/>
+    <hyperlink ref="AW29" r:id="rId223" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1J3C8YFTAUF75"/>
+    <hyperlink ref="C30" r:id="rId224" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
+    <hyperlink ref="G30" r:id="rId225" tooltip="https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B08XM26HKK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J30" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK?psc=1"/>
+    <hyperlink ref="K30" r:id="rId227" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ZUcvmHC5L._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
     <hyperlink ref="M30" r:id="rId229" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N30" r:id="rId230"/>
-    <hyperlink ref="AW30" r:id="rId231" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1J3C8YFTAUF75"/>
-    <hyperlink ref="C31" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
-    <hyperlink ref="G31" r:id="rId233" tooltip="https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B08XM26HKK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId234" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK?psc=1"/>
-    <hyperlink ref="K31" r:id="rId235" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ZUcvmHC5L._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B08XM26HKK"/>
+    <hyperlink ref="AW30" r:id="rId231" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS"/>
+    <hyperlink ref="C31" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B0GSD3NSJC"/>
+    <hyperlink ref="G31" r:id="rId233" tooltip="https://www.amazon.co.jp/stores/%EF%BC%B2%EF%BD%81%EF%BD%99%EF%BD%9A%EF%BD%8F%EF%BD%8E%EF%BD%89%EF%BD%83/page/2A2F6C67-919B-4259-BF3B-3B614F5CF4A6?lp_asin=B0GSD3NSJC&amp;ref_=ast_bln"/>
+    <hyperlink ref="J31" r:id="rId234" tooltip="https://www.amazon.co.jp/dp/B0GSD3NSJC?psc=1"/>
+    <hyperlink ref="K31" r:id="rId235" tooltip="https://images-na.ssl-images-amazon.com/images/I/61lGa5v8mML._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0GSD3NSJC"/>
     <hyperlink ref="M31" r:id="rId237" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N31" r:id="rId238"/>
-    <hyperlink ref="AW31" r:id="rId239" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS"/>
-    <hyperlink ref="C32" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0GSD3NSJC"/>
-    <hyperlink ref="G32" r:id="rId241" tooltip="https://www.amazon.co.jp/stores/%EF%BC%B2%EF%BD%81%EF%BD%99%EF%BD%9A%EF%BD%8F%EF%BD%8E%EF%BD%89%EF%BD%83/page/2A2F6C67-919B-4259-BF3B-3B614F5CF4A6?lp_asin=B0GSD3NSJC&amp;ref_=ast_bln"/>
-    <hyperlink ref="J32" r:id="rId242" tooltip="https://www.amazon.co.jp/dp/B0GSD3NSJC?psc=1"/>
-    <hyperlink ref="K32" r:id="rId243" tooltip="https://images-na.ssl-images-amazon.com/images/I/61lGa5v8mML._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId244" tooltip="https://www.amazon.co.jp/dp/B0GSD3NSJC"/>
+    <hyperlink ref="AW31" r:id="rId239" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23HRKZCC74EMZ"/>
+    <hyperlink ref="C32" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL"/>
+    <hyperlink ref="G32" r:id="rId241" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BCF1JPCL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J32" r:id="rId242" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL?psc=1"/>
+    <hyperlink ref="K32" r:id="rId243" tooltip="https://images-na.ssl-images-amazon.com/images/I/41AW0SKsHqL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId244" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL"/>
     <hyperlink ref="M32" r:id="rId245" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N32" r:id="rId246"/>
-    <hyperlink ref="AW32" r:id="rId247" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23HRKZCC74EMZ"/>
-    <hyperlink ref="C33" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL"/>
-    <hyperlink ref="G33" r:id="rId249" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BCF1JPCL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J33" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL?psc=1"/>
-    <hyperlink ref="K33" r:id="rId251" tooltip="https://images-na.ssl-images-amazon.com/images/I/41AW0SKsHqL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId252" tooltip="https://www.amazon.co.jp/dp/B0BCF1JPCL"/>
+    <hyperlink ref="AW32" r:id="rId247" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17TIQMTOKKTIR"/>
+    <hyperlink ref="C33" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY"/>
+    <hyperlink ref="G33" r:id="rId249" tooltip="https://www.amazon.co.jp/IWA/b/ref=bl_dp_s_web_3622059051?ie=UTF8&amp;node=3622059051&amp;field-lbr_brands_browse-bin=IWA"/>
+    <hyperlink ref="J33" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY?psc=1"/>
+    <hyperlink ref="K33" r:id="rId251" tooltip="https://m.media-amazon.com/images/I/31fosM0+zwL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId252" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY"/>
     <hyperlink ref="M33" r:id="rId253" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N33" r:id="rId254"/>
-    <hyperlink ref="AW33" r:id="rId255" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17TIQMTOKKTIR"/>
-    <hyperlink ref="C34" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY"/>
-    <hyperlink ref="G34" r:id="rId257" tooltip="https://www.amazon.co.jp/IWA/b/ref=bl_dp_s_web_3622059051?ie=UTF8&amp;node=3622059051&amp;field-lbr_brands_browse-bin=IWA"/>
-    <hyperlink ref="J34" r:id="rId258" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY?psc=1"/>
-    <hyperlink ref="K34" r:id="rId259" tooltip="https://m.media-amazon.com/images/I/31fosM0+zwL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B017SAF6OY"/>
-    <hyperlink ref="M34" r:id="rId261" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N34" r:id="rId262"/>
-    <hyperlink ref="C35" r:id="rId263" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB"/>
-    <hyperlink ref="G35" r:id="rId264" tooltip="https://www.amazon.co.jp/stores/FEVORCS/page/2392B65D-91DF-4046-9C5C-89C6E6899285?lp_asin=B0DQSGMXJB&amp;ref_=ast_bln"/>
-    <hyperlink ref="J35" r:id="rId265" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB?psc=1"/>
-    <hyperlink ref="K35" r:id="rId266" tooltip="https://images-na.ssl-images-amazon.com/images/I/616rv7jIiuL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId267" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB"/>
+    <hyperlink ref="C34" r:id="rId255" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB"/>
+    <hyperlink ref="G34" r:id="rId256" tooltip="https://www.amazon.co.jp/stores/FEVORCS/page/2392B65D-91DF-4046-9C5C-89C6E6899285?lp_asin=B0DQSGMXJB&amp;ref_=ast_bln"/>
+    <hyperlink ref="J34" r:id="rId257" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB?psc=1"/>
+    <hyperlink ref="K34" r:id="rId258" tooltip="https://images-na.ssl-images-amazon.com/images/I/616rv7jIiuL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId259" tooltip="https://www.amazon.co.jp/dp/B0DQSGMXJB"/>
+    <hyperlink ref="M34" r:id="rId260" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
+    <hyperlink ref="N34" r:id="rId261"/>
+    <hyperlink ref="AW34" r:id="rId262" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A130FCCM5YKTQ1"/>
+    <hyperlink ref="C35" r:id="rId263" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP"/>
+    <hyperlink ref="G35" r:id="rId264" tooltip="https://www.amazon.co.jp/stores/JIMMY/page/A7D1BFC6-FA2F-4840-A78D-62132A51D89B?lp_asin=B0DGTN1LGP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId265" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP?psc=1"/>
+    <hyperlink ref="K35" r:id="rId266" tooltip="https://images-na.ssl-images-amazon.com/images/I/61q8jT7-5rL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId267" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP"/>
     <hyperlink ref="M35" r:id="rId268" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N35" r:id="rId269"/>
-    <hyperlink ref="AW35" r:id="rId270" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A130FCCM5YKTQ1"/>
-    <hyperlink ref="C36" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP"/>
-    <hyperlink ref="G36" r:id="rId272" tooltip="https://www.amazon.co.jp/stores/JIMMY/page/A7D1BFC6-FA2F-4840-A78D-62132A51D89B?lp_asin=B0DGTN1LGP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J36" r:id="rId273" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP?psc=1"/>
-    <hyperlink ref="K36" r:id="rId274" tooltip="https://images-na.ssl-images-amazon.com/images/I/61q8jT7-5rL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId275" tooltip="https://www.amazon.co.jp/dp/B0DGTN1LGP"/>
+    <hyperlink ref="AW35" r:id="rId270" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A27XS3ZIJF6R09"/>
+    <hyperlink ref="C36" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B087Z4YF8S"/>
+    <hyperlink ref="G36" r:id="rId272" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B087Z4YF8S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J36" r:id="rId273" tooltip="https://www.amazon.co.jp/dp/B087Z4YF8S?psc=1"/>
+    <hyperlink ref="K36" r:id="rId274" tooltip="https://images-na.ssl-images-amazon.com/images/I/51FXGYp5BcL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId275" tooltip="https://www.amazon.co.jp/dp/B087Z4YF8S"/>
     <hyperlink ref="M36" r:id="rId276" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N36" r:id="rId277"/>
-    <hyperlink ref="AW36" r:id="rId278" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A27XS3ZIJF6R09"/>
-    <hyperlink ref="C37" r:id="rId279" tooltip="https://www.amazon.co.jp/dp/B087Z4YF8S"/>
-    <hyperlink ref="G37" r:id="rId280" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B087Z4YF8S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B087Z4YF8S?psc=1"/>
-    <hyperlink ref="K37" r:id="rId282" tooltip="https://images-na.ssl-images-amazon.com/images/I/51FXGYp5BcL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B087Z4YF8S"/>
+    <hyperlink ref="AW36" r:id="rId278" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JLEXPXXTRB24"/>
+    <hyperlink ref="C37" r:id="rId279" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD"/>
+    <hyperlink ref="G37" r:id="rId280" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JIGOO"/>
+    <hyperlink ref="J37" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD?psc=1"/>
+    <hyperlink ref="K37" r:id="rId282" tooltip="https://images-na.ssl-images-amazon.com/images/I/71332p8jV1L._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD"/>
     <hyperlink ref="M37" r:id="rId284" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N37" r:id="rId285"/>
-    <hyperlink ref="AW37" r:id="rId286" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JLEXPXXTRB24"/>
-    <hyperlink ref="C38" r:id="rId287" tooltip="https://www.amazon.co.jp/dp/B0H6FF5LHZ"/>
-    <hyperlink ref="G38" r:id="rId288" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=pronala"/>
-    <hyperlink ref="J38" r:id="rId289" tooltip="https://www.amazon.co.jp/dp/B0H6FF5LHZ?psc=1"/>
-    <hyperlink ref="K38" r:id="rId290" tooltip="https://images-na.ssl-images-amazon.com/images/I/711Q4UmnGjL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId291" tooltip="https://www.amazon.co.jp/dp/B0H6FF5LHZ"/>
+    <hyperlink ref="AW37" r:id="rId286" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UV5G74OMRQ0L"/>
+    <hyperlink ref="C38" r:id="rId287" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71"/>
+    <hyperlink ref="G38" r:id="rId288" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81"/>
+    <hyperlink ref="J38" r:id="rId289" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71?psc=1"/>
+    <hyperlink ref="K38" r:id="rId290" tooltip="https://images-na.ssl-images-amazon.com/images/I/41t94rJieZL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId291" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71"/>
     <hyperlink ref="M38" r:id="rId292" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N38" r:id="rId293"/>
-    <hyperlink ref="AW38" r:id="rId294" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TBQ5YA5MO311"/>
-    <hyperlink ref="C39" r:id="rId295" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD"/>
-    <hyperlink ref="G39" r:id="rId296" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JIGOO"/>
-    <hyperlink ref="J39" r:id="rId297" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD?psc=1"/>
-    <hyperlink ref="K39" r:id="rId298" tooltip="https://images-na.ssl-images-amazon.com/images/I/71332p8jV1L._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId299" tooltip="https://www.amazon.co.jp/dp/B0DW45FNFD"/>
+    <hyperlink ref="AW38" r:id="rId294" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XC24KSDSD196"/>
+    <hyperlink ref="C39" r:id="rId295" tooltip="https://www.amazon.co.jp/dp/B0DTXHF87N"/>
+    <hyperlink ref="G39" r:id="rId296" tooltip="https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DTXHF87N&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J39" r:id="rId297" tooltip="https://www.amazon.co.jp/dp/B0DTXHF87N?psc=1"/>
+    <hyperlink ref="K39" r:id="rId298" tooltip="https://images-na.ssl-images-amazon.com/images/I/616ONjp63mL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId299" tooltip="https://www.amazon.co.jp/dp/B0DTXHF87N"/>
     <hyperlink ref="M39" r:id="rId300" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N39" r:id="rId301"/>
-    <hyperlink ref="AW39" r:id="rId302" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UV5G74OMRQ0L"/>
-    <hyperlink ref="C40" r:id="rId303" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71"/>
-    <hyperlink ref="G40" r:id="rId304" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E3%83%8E%E3%83%BC%E3%83%96%E3%83%A9%E3%83%B3%E3%83%89%E5%93%81"/>
-    <hyperlink ref="J40" r:id="rId305" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71?psc=1"/>
-    <hyperlink ref="K40" r:id="rId306" tooltip="https://images-na.ssl-images-amazon.com/images/I/41t94rJieZL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId307" tooltip="https://www.amazon.co.jp/dp/B0GTTTTP71"/>
+    <hyperlink ref="AW39" r:id="rId302" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES"/>
+    <hyperlink ref="C40" r:id="rId303" tooltip="https://www.amazon.co.jp/dp/B086D6FKJJ"/>
+    <hyperlink ref="G40" r:id="rId304" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B086D6FKJJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J40" r:id="rId305" tooltip="https://www.amazon.co.jp/dp/B086D6FKJJ?psc=1"/>
+    <hyperlink ref="K40" r:id="rId306" tooltip="https://images-na.ssl-images-amazon.com/images/I/51m1MS9FICL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId307" tooltip="https://www.amazon.co.jp/dp/B086D6FKJJ"/>
     <hyperlink ref="M40" r:id="rId308" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N40" r:id="rId309"/>
-    <hyperlink ref="AW40" r:id="rId310" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XC24KSDSD196"/>
-    <hyperlink ref="C41" r:id="rId311" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S"/>
-    <hyperlink ref="G41" r:id="rId312" tooltip="https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0DY61ZS3S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId313" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S?psc=1"/>
-    <hyperlink ref="K41" r:id="rId314" tooltip="https://images-na.ssl-images-amazon.com/images/I/31dizVJn3lL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId315" tooltip="https://www.amazon.co.jp/dp/B0DY61ZS3S"/>
+    <hyperlink ref="AW40" r:id="rId310" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQU7G7SXPENAQ"/>
+    <hyperlink ref="C41" r:id="rId311" tooltip="https://www.amazon.co.jp/dp/B00NII5XEE"/>
+    <hyperlink ref="G41" r:id="rId312" tooltip="https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B00NII5XEE&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId313" tooltip="https://www.amazon.co.jp/dp/B00NII5XEE?psc=1"/>
+    <hyperlink ref="K41" r:id="rId314" tooltip="https://images-na.ssl-images-amazon.com/images/I/51x2VvwoIaL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId315" tooltip="https://www.amazon.co.jp/dp/B00NII5XEE"/>
     <hyperlink ref="M41" r:id="rId316" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N41" r:id="rId317"/>
-    <hyperlink ref="AW41" r:id="rId318" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ZTSKKP4W4CQ6"/>
-    <hyperlink ref="C42" r:id="rId319" tooltip="https://www.amazon.co.jp/dp/B0DTXHF87N"/>
-    <hyperlink ref="G42" r:id="rId320" tooltip="https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DTXHF87N&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J42" r:id="rId321" tooltip="https://www.amazon.co.jp/dp/B0DTXHF87N?psc=1"/>
-    <hyperlink ref="K42" r:id="rId322" tooltip="https://images-na.ssl-images-amazon.com/images/I/616ONjp63mL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId323" tooltip="https://www.amazon.co.jp/dp/B0DTXHF87N"/>
+    <hyperlink ref="AW41" r:id="rId318" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS"/>
+    <hyperlink ref="C42" r:id="rId319" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4"/>
+    <hyperlink ref="G42" r:id="rId320" tooltip="https://www.amazon.co.jp/Neping/b/ref=bl_dp_s_web_23533992051?ie=UTF8&amp;node=23533992051&amp;field-lbr_brands_browse-bin=Neping"/>
+    <hyperlink ref="J42" r:id="rId321" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4?psc=1"/>
+    <hyperlink ref="K42" r:id="rId322" tooltip="https://images-na.ssl-images-amazon.com/images/I/31bjNOyZF4L._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId323" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4"/>
     <hyperlink ref="M42" r:id="rId324" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N42" r:id="rId325"/>
-    <hyperlink ref="AW42" r:id="rId326" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES"/>
-    <hyperlink ref="C43" r:id="rId327" tooltip="https://www.amazon.co.jp/dp/B0HJBYGLLS"/>
-    <hyperlink ref="G43" r:id="rId328" tooltip="https://www.amazon.co.jp/stores/Yizibuur/page/16D746F6-5F31-4921-AAB0-B9944FFD45C3?lp_asin=B0HJBYGLLS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId329" tooltip="https://www.amazon.co.jp/dp/B0HJBYGLLS?psc=1"/>
-    <hyperlink ref="K43" r:id="rId330" tooltip="https://m.media-amazon.com/images/I/41D9mkEdSsL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId331" tooltip="https://www.amazon.co.jp/dp/B0HJBYGLLS"/>
+    <hyperlink ref="AW42" r:id="rId326" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJHJPPEGEZ4DJ"/>
+    <hyperlink ref="C43" r:id="rId327" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
+    <hyperlink ref="G43" r:id="rId328" tooltip="https://www.amazon.co.jp/stores/%E3%82%A8%E3%82%B3%E3%82%B8%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%95/page/92446153-5DF5-46D6-8BDE-A3C30B3D3E3A?lp_asin=B0DR1YK9LS&amp;ref_=ast_bln"/>
+    <hyperlink ref="J43" r:id="rId329" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1"/>
+    <hyperlink ref="K43" r:id="rId330" tooltip="https://images-na.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId331" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
     <hyperlink ref="M43" r:id="rId332" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N43" r:id="rId333"/>
-    <hyperlink ref="AW43" r:id="rId334" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2Q4HC9SZPWZ92"/>
-    <hyperlink ref="C44" r:id="rId335" tooltip="https://www.amazon.co.jp/dp/B086D6FKJJ"/>
-    <hyperlink ref="G44" r:id="rId336" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B086D6FKJJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId337" tooltip="https://www.amazon.co.jp/dp/B086D6FKJJ?psc=1"/>
-    <hyperlink ref="K44" r:id="rId338" tooltip="https://images-na.ssl-images-amazon.com/images/I/51m1MS9FICL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId339" tooltip="https://www.amazon.co.jp/dp/B086D6FKJJ"/>
+    <hyperlink ref="AW43" r:id="rId334" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A13LYSKWCMFUWB"/>
+    <hyperlink ref="C44" r:id="rId335" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
+    <hyperlink ref="G44" r:id="rId336" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0H6BMMJJ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId337" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1"/>
+    <hyperlink ref="K44" r:id="rId338" tooltip="https://m.media-amazon.com/images/I/217kOnSQp6L._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId339" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
     <hyperlink ref="M44" r:id="rId340" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
     <hyperlink ref="N44" r:id="rId341"/>
-    <hyperlink ref="AW44" r:id="rId342" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQU7G7SXPENAQ"/>
-    <hyperlink ref="C45" r:id="rId343" tooltip="https://www.amazon.co.jp/dp/B00NII5XEE"/>
-    <hyperlink ref="G45" r:id="rId344" tooltip="https://www.amazon.co.jp/stores/%E3%83%AC%E3%82%A4%E3%82%B3%E3%83%83%E3%83%97%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9E%E3%82%A4%E3%82%B1%E3%83%AB/page/8D2E5A72-95D7-45A9-9483-BB2A10DE66BE?lp_asin=B00NII5XEE&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId345" tooltip="https://www.amazon.co.jp/dp/B00NII5XEE?psc=1"/>
-    <hyperlink ref="K45" r:id="rId346" tooltip="https://images-na.ssl-images-amazon.com/images/I/51x2VvwoIaL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId347" tooltip="https://www.amazon.co.jp/dp/B00NII5XEE"/>
-    <hyperlink ref="M45" r:id="rId348" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N45" r:id="rId349"/>
-    <hyperlink ref="AW45" r:id="rId350" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1TM9KKRIQ3TGS"/>
-    <hyperlink ref="C46" r:id="rId351" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4"/>
-    <hyperlink ref="G46" r:id="rId352" tooltip="https://www.amazon.co.jp/Neping/b/ref=bl_dp_s_web_23533992051?ie=UTF8&amp;node=23533992051&amp;field-lbr_brands_browse-bin=Neping"/>
-    <hyperlink ref="J46" r:id="rId353" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4?psc=1"/>
-    <hyperlink ref="K46" r:id="rId354" tooltip="https://images-na.ssl-images-amazon.com/images/I/31bjNOyZF4L._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId355" tooltip="https://www.amazon.co.jp/dp/B0DH8B8TM4"/>
-    <hyperlink ref="M46" r:id="rId356" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N46" r:id="rId357"/>
-    <hyperlink ref="AW46" r:id="rId358" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJHJPPEGEZ4DJ"/>
-    <hyperlink ref="C47" r:id="rId359" tooltip="https://www.amazon.co.jp/dp/B0GGHC2648"/>
-    <hyperlink ref="G47" r:id="rId360" tooltip="https://www.amazon.co.jp/stores/Cociliye/page/A132712C-622E-4322-A6B1-CC60DBFB2A1C?lp_asin=B0GGHCSSRC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId361" tooltip="https://www.amazon.co.jp/dp/B0GGHC2648?psc=1"/>
-    <hyperlink ref="K47" r:id="rId362" tooltip="https://images-na.ssl-images-amazon.com/images/I/7116SveneNL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId363" tooltip="https://www.amazon.co.jp/dp/B0GGHC2648"/>
-    <hyperlink ref="M47" r:id="rId364" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N47" r:id="rId365"/>
-    <hyperlink ref="AW47" r:id="rId366" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UMUHBLLQ740B"/>
-    <hyperlink ref="C48" r:id="rId367" tooltip="https://www.amazon.co.jp/dp/B0GFMNZH8L"/>
-    <hyperlink ref="G48" r:id="rId368" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=JUELREOU"/>
-    <hyperlink ref="J48" r:id="rId369" tooltip="https://www.amazon.co.jp/dp/B0GFMNZH8L?psc=1"/>
-    <hyperlink ref="K48" r:id="rId370" tooltip="https://m.media-amazon.com/images/I/41pnZeYlEhL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId371" tooltip="https://www.amazon.co.jp/dp/B0GFMNZH8L"/>
-    <hyperlink ref="M48" r:id="rId372" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N48" r:id="rId373"/>
-    <hyperlink ref="AW48" r:id="rId374" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1VJKLQTDJXYI3"/>
-    <hyperlink ref="C49" r:id="rId375" tooltip="https://www.amazon.co.jp/dp/B0GCFFRYMW"/>
-    <hyperlink ref="G49" r:id="rId376" tooltip="https://www.amazon.co.jp/stores/%E9%AB%98%E5%93%81%E8%B3%AA%E3%81%A7%E6%89%8B%E9%A0%83%E3%81%AA%E4%BE%A1%E6%A0%BC%E3%81%AE%E5%95%86%E5%93%81%E3%82%92%E3%81%8A%E5%B1%8A%E3%81%91%E3%81%97%E3%81%BE%E3%81%99%E3%80%82/page/CBB43826-CEEB-4FCD-9B7C-350E46DDAFE0?lp_asin=B0GCFFRYMW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId377" tooltip="https://www.amazon.co.jp/dp/B0GCFFRYMW?psc=1"/>
-    <hyperlink ref="K49" r:id="rId378" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ajaiqPPWL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId379" tooltip="https://www.amazon.co.jp/dp/B0GCFFRYMW"/>
-    <hyperlink ref="M49" r:id="rId380" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N49" r:id="rId381"/>
-    <hyperlink ref="AW49" r:id="rId382" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23ENIU0LZSTG6"/>
-    <hyperlink ref="C50" r:id="rId383" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
-    <hyperlink ref="G50" r:id="rId384" tooltip="https://www.amazon.co.jp/stores/%E3%82%A8%E3%82%B3%E3%82%B8%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%95/page/92446153-5DF5-46D6-8BDE-A3C30B3D3E3A?lp_asin=B0DR1YK9LS&amp;ref_=ast_bln"/>
-    <hyperlink ref="J50" r:id="rId385" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS?psc=1"/>
-    <hyperlink ref="K50" r:id="rId386" tooltip="https://images-na.ssl-images-amazon.com/images/I/71p2ybmlLFL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId387" tooltip="https://www.amazon.co.jp/dp/B0DR1YK9LS"/>
-    <hyperlink ref="M50" r:id="rId388" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N50" r:id="rId389"/>
-    <hyperlink ref="AW50" r:id="rId390" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A13LYSKWCMFUWB"/>
-    <hyperlink ref="C51" r:id="rId391" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
-    <hyperlink ref="G51" r:id="rId392" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0H6BMMJJ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId393" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2?psc=1"/>
-    <hyperlink ref="K51" r:id="rId394" tooltip="https://m.media-amazon.com/images/I/217kOnSQp6L._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId395" tooltip="https://www.amazon.co.jp/dp/B0H6BMMJJ2"/>
-    <hyperlink ref="M51" r:id="rId396" tooltip="https://www.amazon.co.jp/b?node=5248688051"/>
-    <hyperlink ref="N51" r:id="rId397"/>
-    <hyperlink ref="AW51" r:id="rId398" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A73TY2PE3Z2RH"/>
+    <hyperlink ref="AW44" r:id="rId342" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A73TY2PE3Z2RH"/>
   </hyperlinks>
-  <drawing r:id="rId399"/>
+  <drawing r:id="rId343"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19152,7 +17484,7 @@
         <v>19413.159781761497</v>
       </c>
       <c r="G2" s="19">
-        <v>0.1683727034120735</v>
+        <v>0.1704077566741931</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19173,7 +17505,7 @@
         <v>10461.098225876243</v>
       </c>
       <c r="G3" s="19">
-        <v>0.30328083989501314</v>
+        <v>0.30694647363527694</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19194,7 +17526,7 @@
         <v>7744.4902042517715</v>
       </c>
       <c r="G4" s="19">
-        <v>0.3148293963254593</v>
+        <v>0.3186346128303892</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19215,7 +17547,7 @@
         <v>36870.055555555555</v>
       </c>
       <c r="G5" s="19">
-        <v>0.011811023622047244</v>
+        <v>0.011953778722273874</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19236,7 +17568,7 @@
         <v>11817.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.022440944881889763</v>
+        <v>0.02271217957232036</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19257,7 +17589,7 @@
         <v>6999.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.03727034120734908</v>
+        <v>0.03772081285695311</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19278,7 +17610,7 @@
         <v>24347.484848484848</v>
       </c>
       <c r="G8" s="19">
-        <v>0.008661417322834646</v>
+        <v>0.008766104396334174</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19299,7 +17631,7 @@
         <v>9909.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.015354330708661417</v>
+        <v>0.015539912338956036</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19320,7 +17652,7 @@
         <v>5980.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.02230971128608924</v>
+        <v>0.02257935980873954</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19341,7 +17673,7 @@
         <v>11999.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.00984251968503937</v>
+        <v>0.009961482268561563</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19362,7 +17694,7 @@
         <v>5164.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.020866141732283464</v>
+        <v>0.02111834240935051</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19383,7 +17715,7 @@
         <v>13099.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.005905511811023622</v>
+        <v>0.005976889361136937</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19404,7 +17736,7 @@
         <v>15494.942857142858</v>
       </c>
       <c r="G14" s="19">
-        <v>0.004593175853018373</v>
+        <v>0.004648691725328729</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19425,298 +17757,151 @@
         <v>8999.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.007480314960629921</v>
+        <v>0.007570726524106787</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>パナソニック(Panasonic)</t>
+          <t>EFSHREE</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C16" s="13">
-        <v>428800</v>
+        <v>420564</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13">
-        <v>26800.0</v>
+        <v>4164.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.002099737532808399</v>
+        <v>0.013414796121662903</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>EFSHREE</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="B17" s="13">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="C17" s="13">
-        <v>420564</v>
+        <v>287280</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13">
-        <v>4164.0</v>
+        <v>7980.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.013254593175853018</v>
+        <v>0.00478151148890955</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>IWA</t>
         </is>
       </c>
       <c r="B18" s="13">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="C18" s="13">
-        <v>287280</v>
+        <v>140530</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13">
-        <v>7980.0</v>
+        <v>1495.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.004724409448818898</v>
+        <v>0.012485057776597157</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>IWA</t>
+          <t>FEVORCS</t>
         </is>
       </c>
       <c r="B19" s="13">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="C19" s="13">
-        <v>140530</v>
+        <v>127400</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13">
-        <v>1495.0</v>
+        <v>9800.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.012335958005249344</v>
+        <v>0.0017266569265506708</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>FEVORCS</t>
+          <t>ノーブランド品</t>
         </is>
       </c>
       <c r="B20" s="13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C20" s="13">
-        <v>127400</v>
+        <v>71865</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13">
-        <v>9800.0</v>
+        <v>7985.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.0017060367454068241</v>
+        <v>0.0011953778722273874</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>pronala</t>
+          <t>Neping</t>
         </is>
       </c>
       <c r="B21" s="13">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C21" s="13">
-        <v>80224</v>
+        <v>23786</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13">
-        <v>3488.0</v>
+        <v>1699.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.0030183727034120734</v>
+        <v>0.0018594766901314915</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>ノーブランド品</t>
+          <t>エコジー</t>
         </is>
       </c>
       <c r="B22" s="13">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C22" s="13">
-        <v>71865</v>
+        <v>0</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
-      <c r="F22" s="13">
-        <v>7985.0</v>
-      </c>
+      <c r="F22" s="13"/>
       <c r="G22" s="19">
-        <v>0.0011811023622047244</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Dyson(ダイソン)</t>
-        </is>
-      </c>
-      <c r="B23" s="13">
-        <v>14</v>
-      </c>
-      <c r="C23" s="13">
-        <v>69720</v>
-      </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13">
-        <v>4980.0</v>
-      </c>
-      <c r="G23" s="19">
-        <v>0.001837270341207349</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Yizibuur</t>
-        </is>
-      </c>
-      <c r="B24" s="13">
-        <v>35</v>
-      </c>
-      <c r="C24" s="13">
-        <v>50540</v>
-      </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13">
-        <v>1444.0</v>
-      </c>
-      <c r="G24" s="19">
-        <v>0.004593175853018373</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Neping</t>
-        </is>
-      </c>
-      <c r="B25" s="13">
-        <v>14</v>
-      </c>
-      <c r="C25" s="13">
-        <v>23786</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13">
-        <v>1699.0</v>
-      </c>
-      <c r="G25" s="19">
-        <v>0.001837270341207349</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Cociliye</t>
-        </is>
-      </c>
-      <c r="B26" s="13">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13">
-        <v>2388</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13">
-        <v>2388.0</v>
-      </c>
-      <c r="G26" s="19">
-        <v>0.00013123359580052493</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU</t>
-        </is>
-      </c>
-      <c r="B27" s="13">
-        <v>1</v>
-      </c>
-      <c r="C27" s="13">
-        <v>1144</v>
-      </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13">
-        <v>1144.0</v>
-      </c>
-      <c r="G27" s="19">
-        <v>0.00013123359580052493</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Vailaipupy</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13">
-        <v>498</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13">
-        <v>498.0</v>
-      </c>
-      <c r="G28" s="19">
-        <v>0.00013123359580052493</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>エコジー</t>
-        </is>
-      </c>
-      <c r="B29" s="13">
-        <v>0</v>
-      </c>
-      <c r="C29" s="13">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -19728,7 +17913,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19792,7 +17977,7 @@
         <v>19800.0</v>
       </c>
       <c r="G2" s="19">
-        <v>0.16128608923884513</v>
+        <v>0.1632354894408288</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19813,7 +17998,7 @@
         <v>10461.098225876243</v>
       </c>
       <c r="G3" s="19">
-        <v>0.30328083989501314</v>
+        <v>0.30694647363527694</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19834,7 +18019,7 @@
         <v>7348.0</v>
       </c>
       <c r="G4" s="19">
-        <v>0.2648293963254593</v>
+        <v>0.26803028290609643</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19855,7 +18040,7 @@
         <v>36345.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.01010498687664042</v>
+        <v>0.010227121795723203</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19876,7 +18061,7 @@
         <v>11817.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.022440944881889763</v>
+        <v>0.02271217957232036</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19897,7 +18082,7 @@
         <v>6999.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.03727034120734908</v>
+        <v>0.03772081285695311</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19918,7 +18103,7 @@
         <v>24665.666666666668</v>
       </c>
       <c r="G8" s="19">
-        <v>0.007086614173228346</v>
+        <v>0.007172267233364325</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19939,7 +18124,7 @@
         <v>9909.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.015354330708661417</v>
+        <v>0.015539912338956036</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19960,7 +18145,7 @@
         <v>7945.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.01837270341207349</v>
+        <v>0.018594766901314917</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19981,7 +18166,7 @@
         <v>10727.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.013123359580052493</v>
+        <v>0.013281976358082082</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20002,7 +18187,7 @@
         <v>5980.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.02230971128608924</v>
+        <v>0.02257935980873954</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20023,7 +18208,7 @@
         <v>11999.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.00984251968503937</v>
+        <v>0.009961482268561563</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20044,7 +18229,7 @@
         <v>5164.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.020866141732283464</v>
+        <v>0.02111834240935051</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20065,7 +18250,7 @@
         <v>5251.690647482014</v>
       </c>
       <c r="G15" s="19">
-        <v>0.018241469816272966</v>
+        <v>0.018461947137734094</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20086,7 +18271,7 @@
         <v>14572.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.006430446194225722</v>
+        <v>0.006508168415460221</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20107,7 +18292,7 @@
         <v>39980.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.0017060367454068241</v>
+        <v>0.0017266569265506708</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20128,527 +18313,380 @@
         <v>8999.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.007480314960629921</v>
+        <v>0.007570726524106787</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>パル商店【適格請求書発行事業者】</t>
+          <t>YFS-JP</t>
         </is>
       </c>
       <c r="B19" s="13">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C19" s="13">
-        <v>428800</v>
+        <v>420564</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13">
-        <v>26800.0</v>
+        <v>4164.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.002099737532808399</v>
+        <v>0.013414796121662903</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>YFS-JP</t>
+          <t>Qifan shop</t>
         </is>
       </c>
       <c r="B20" s="13">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="C20" s="13">
-        <v>420564</v>
+        <v>382483</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13">
-        <v>4164.0</v>
+        <v>14166.037037037036</v>
       </c>
       <c r="G20" s="19">
-        <v>0.013254593175853018</v>
+        <v>0.0035861336166821624</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Qifan shop</t>
+          <t>【公式】halfilm market - インボイス対応 -</t>
         </is>
       </c>
       <c r="B21" s="13">
         <v>27</v>
       </c>
       <c r="C21" s="13">
-        <v>382483</v>
+        <v>324000</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13">
-        <v>14166.037037037036</v>
+        <v>12000.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.003543307086614173</v>
+        <v>0.0035861336166821624</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>【公式】halfilm market - インボイス対応 -</t>
+          <t>Megastar Store</t>
         </is>
       </c>
       <c r="B22" s="13">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C22" s="13">
-        <v>324000</v>
+        <v>287280</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13">
-        <v>12000.0</v>
+        <v>7980.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.003543307086614173</v>
+        <v>0.00478151148890955</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Megastar Store</t>
+          <t>Jimmy-JP</t>
         </is>
       </c>
       <c r="B23" s="13">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C23" s="13">
-        <v>287280</v>
+        <v>274988</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13">
-        <v>7980.0</v>
+        <v>22915.666666666668</v>
       </c>
       <c r="G23" s="19">
-        <v>0.004724409448818898</v>
+        <v>0.00159383716296985</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Jimmy-JP</t>
+          <t>FASネット部門(古物商許可、インボイス制度登録)</t>
         </is>
       </c>
       <c r="B24" s="13">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C24" s="13">
-        <v>274988</v>
+        <v>236740</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13">
-        <v>22915.666666666668</v>
+        <v>8455.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.0015748031496062992</v>
+        <v>0.003718953380262983</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>FASネット部門(古物商許可、インボイス制度登録)</t>
+          <t>トラストネット卸（すり替え防止対策店、適格請求書発行事業者）</t>
         </is>
       </c>
       <c r="B25" s="13">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C25" s="13">
-        <v>236740</v>
+        <v>200200</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13">
-        <v>8455.0</v>
+        <v>18200.0</v>
       </c>
       <c r="G25" s="19">
-        <v>0.003674540682414698</v>
+        <v>0.001461017399389029</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>トラストネット卸（すり替え防止対策店、適格請求書発行事業者）</t>
+          <t>モリハウス</t>
         </is>
       </c>
       <c r="B26" s="13">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C26" s="13">
-        <v>200200</v>
+        <v>197964</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13">
-        <v>18200.0</v>
+        <v>6826.3448275862065</v>
       </c>
       <c r="G26" s="19">
-        <v>0.0014435695538057743</v>
+        <v>0.003851773143843804</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>モリハウス</t>
+          <t>ネロビア</t>
         </is>
       </c>
       <c r="B27" s="13">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C27" s="13">
-        <v>197964</v>
+        <v>174720</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
       <c r="F27" s="13">
-        <v>6826.3448275862065</v>
+        <v>12480.0</v>
       </c>
       <c r="G27" s="19">
-        <v>0.003805774278215223</v>
+        <v>0.0018594766901314915</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>ネロビア</t>
+          <t>天興株式会社-JP</t>
         </is>
       </c>
       <c r="B28" s="13">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C28" s="13">
-        <v>174720</v>
+        <v>159840</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13">
-        <v>12480.0</v>
+        <v>19980.0</v>
       </c>
       <c r="G28" s="19">
-        <v>0.001837270341207349</v>
+        <v>0.0010625581086465667</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>天興株式会社-JP</t>
+          <t>合同会社レステリオ</t>
         </is>
       </c>
       <c r="B29" s="13">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C29" s="13">
-        <v>159840</v>
+        <v>151680</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13">
-        <v>19980.0</v>
+        <v>9480.0</v>
       </c>
       <c r="G29" s="19">
-        <v>0.0010498687664041995</v>
+        <v>0.0021251162172931334</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>合同会社レステリオ</t>
+          <t>Koda Electrical</t>
         </is>
       </c>
       <c r="B30" s="13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C30" s="13">
-        <v>151680</v>
+        <v>127400</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13">
-        <v>9480.0</v>
+        <v>9800.0</v>
       </c>
       <c r="G30" s="19">
-        <v>0.002099737532808399</v>
+        <v>0.0017266569265506708</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Koda Electrical</t>
+          <t>スケチヨ商店(適格請求書発行事業者)</t>
         </is>
       </c>
       <c r="B31" s="13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C31" s="13">
-        <v>127400</v>
+        <v>97500</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="13">
-        <v>9800.0</v>
+        <v>6500.0</v>
       </c>
       <c r="G31" s="19">
-        <v>0.0017060367454068241</v>
+        <v>0.0019922964537123122</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>スケチヨ商店(適格請求書発行事業者)</t>
+          <t>JianShengTool</t>
         </is>
       </c>
       <c r="B32" s="13">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C32" s="13">
-        <v>97500</v>
+        <v>71865</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="13">
-        <v>6500.0</v>
+        <v>7985.0</v>
       </c>
       <c r="G32" s="19">
-        <v>0.001968503937007874</v>
+        <v>0.0011953778722273874</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>配送3～11日以内PronalaShop-JP</t>
+          <t>makana1001</t>
         </is>
       </c>
       <c r="B33" s="13">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C33" s="13">
-        <v>80224</v>
+        <v>41820</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="F33" s="13">
-        <v>3488.0</v>
+        <v>6970.0</v>
       </c>
       <c r="G33" s="19">
-        <v>0.0030183727034120734</v>
+        <v>0.000796918581484925</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>JianShengTool</t>
+          <t>配送3～11日以内Neping Shop-JP</t>
         </is>
       </c>
       <c r="B34" s="13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C34" s="13">
-        <v>71865</v>
+        <v>23786</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
       <c r="F34" s="13">
-        <v>7985.0</v>
+        <v>1699.0</v>
       </c>
       <c r="G34" s="19">
-        <v>0.0011811023622047244</v>
+        <v>0.0018594766901314915</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>OMITSU</t>
+          <t>Solesenyue</t>
         </is>
       </c>
       <c r="B35" s="13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C35" s="13">
-        <v>69720</v>
+        <v>0</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
-      <c r="F35" s="13">
-        <v>4980.0</v>
-      </c>
+      <c r="F35" s="13"/>
       <c r="G35" s="19">
-        <v>0.001837270341207349</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>XiZou e-commerce(跟卖必下单投诉）</t>
+          <t>イートレンド [適格請求書発行事業者登録済]</t>
         </is>
       </c>
       <c r="B36" s="13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C36" s="13">
-        <v>50540</v>
+        <v>0</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
-      <c r="F36" s="13">
-        <v>1444.0</v>
-      </c>
+      <c r="F36" s="13"/>
       <c r="G36" s="19">
-        <v>0.004593175853018373</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>makana1001</t>
-        </is>
-      </c>
-      <c r="B37" s="13">
-        <v>6</v>
-      </c>
-      <c r="C37" s="13">
-        <v>41820</v>
-      </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13">
-        <v>6970.0</v>
-      </c>
-      <c r="G37" s="19">
-        <v>0.0007874015748031496</v>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>配送3～11日以内Neping Shop-JP</t>
-        </is>
-      </c>
-      <c r="B38" s="13">
-        <v>14</v>
-      </c>
-      <c r="C38" s="13">
-        <v>23786</v>
-      </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13">
-        <v>1699.0</v>
-      </c>
-      <c r="G38" s="19">
-        <v>0.001837270341207349</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐Cociliye Kinnei shop（通常、7〜10日配達されます）</t>
-        </is>
-      </c>
-      <c r="B39" s="13">
-        <v>1</v>
-      </c>
-      <c r="C39" s="13">
-        <v>2388</v>
-      </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13">
-        <v>2388.0</v>
-      </c>
-      <c r="G39" s="19">
-        <v>0.00013123359580052493</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>JUELREOU（通常、5〜10日配達されます）</t>
-        </is>
-      </c>
-      <c r="B40" s="13">
-        <v>1</v>
-      </c>
-      <c r="C40" s="13">
-        <v>1144</v>
-      </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13">
-        <v>1144.0</v>
-      </c>
-      <c r="G40" s="19">
-        <v>0.00013123359580052493</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Shugeng e-commerce（通常7〜10日配達されます）⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B41" s="13">
-        <v>1</v>
-      </c>
-      <c r="C41" s="13">
-        <v>498</v>
-      </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13">
-        <v>498.0</v>
-      </c>
-      <c r="G41" s="19">
-        <v>0.00013123359580052493</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>Solesenyue</t>
-        </is>
-      </c>
-      <c r="B42" s="13">
-        <v>0</v>
-      </c>
-      <c r="C42" s="13">
-        <v>0</v>
-      </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>イートレンド [適格請求書発行事業者登録済]</t>
-        </is>
-      </c>
-      <c r="B43" s="13">
-        <v>0</v>
-      </c>
-      <c r="C43" s="13">
-        <v>0</v>
-      </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="19">
         <v>0.0</v>
       </c>
     </row>
